--- a/25-26-Bahar-Final-OİS.xlsx
+++ b/25-26-Bahar-Final-OİS.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E71CD82-739D-466B-A5B9-0759D4B05433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A43D653B-488F-4960-994E-7EDFF6F9E803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="582">
   <si>
     <t>Ders Kodu</t>
   </si>
@@ -1033,9 +1033,6 @@
     <t>Dr. Öğr. Üyesi Ceren İlkay Soylu Küçükgöncü</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Bİrsen Özalp</t>
-  </si>
-  <si>
     <t>Dr. Öğr. Üyesi Ferhat Kutlu</t>
   </si>
   <si>
@@ -1147,84 +1144,87 @@
     <t>MIS204</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Öğr. Üyesi Hazar ALTINBAŞ </t>
+  </si>
+  <si>
+    <t>MIS308</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Adil Gürsel Karaçor</t>
+  </si>
+  <si>
+    <t>MIS306</t>
+  </si>
+  <si>
+    <t>F-404</t>
+  </si>
+  <si>
+    <t>MIS208</t>
+  </si>
+  <si>
+    <t>ECON134</t>
+  </si>
+  <si>
+    <t>F-102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Öğr. Üyesi Melike Karatay </t>
+  </si>
+  <si>
+    <t>MIS402</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Mehmet Gürel Tekelioğlu</t>
+  </si>
+  <si>
+    <t>MIS460</t>
+  </si>
+  <si>
+    <t>MIS206</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Ceyda Aysuna Türkyılmaz</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Onur Yamaner</t>
+  </si>
+  <si>
+    <t>MIS104</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Cevahir Parlak</t>
+  </si>
+  <si>
+    <t>Doç.Dr. Nihan Akıncılar Köseoğlu</t>
+  </si>
+  <si>
+    <t>Arş.Gör. Rümeysa Karagöz</t>
+  </si>
+  <si>
+    <t>MIS354</t>
+  </si>
+  <si>
+    <t>YBS</t>
+  </si>
+  <si>
+    <t>HIST103</t>
+  </si>
+  <si>
+    <t>YBS104</t>
+  </si>
+  <si>
+    <t>ECON141</t>
+  </si>
+  <si>
+    <t>YBS102</t>
+  </si>
+  <si>
+    <t>F-304</t>
+  </si>
+  <si>
     <t>Dr. Öğr. Üyesi Melike Karatay</t>
   </si>
   <si>
-    <t>MIS308</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Adil Gürsel Karaçor</t>
-  </si>
-  <si>
-    <t>MIS306</t>
-  </si>
-  <si>
-    <t>F-404</t>
-  </si>
-  <si>
-    <t>MIS208</t>
-  </si>
-  <si>
-    <t>ECON134</t>
-  </si>
-  <si>
-    <t>F-102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Öğr. Üyesi Melike Karatay </t>
-  </si>
-  <si>
-    <t>MIS402</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Mehmet Gürel Tekelioğlu</t>
-  </si>
-  <si>
-    <t>MIS460</t>
-  </si>
-  <si>
-    <t>MIS206</t>
-  </si>
-  <si>
-    <t>Prof. Dr. Ceyda Aysuna Türkyılmaz</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Onur Yamaner</t>
-  </si>
-  <si>
-    <t>MIS104</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Cevahir Parlak</t>
-  </si>
-  <si>
-    <t>Doç.Dr. Nihan Akıncılar Köseoğlu</t>
-  </si>
-  <si>
-    <t>Arş.Gör. Rümeysa Karagöz</t>
-  </si>
-  <si>
-    <t>MIS354</t>
-  </si>
-  <si>
-    <t>YBS</t>
-  </si>
-  <si>
-    <t>HIST103</t>
-  </si>
-  <si>
-    <t>YBS104</t>
-  </si>
-  <si>
-    <t>ECON141</t>
-  </si>
-  <si>
-    <t>YBS102</t>
-  </si>
-  <si>
-    <t>F-304</t>
-  </si>
-  <si>
     <t>YBS106</t>
   </si>
   <si>
@@ -1417,150 +1417,150 @@
     <t>Arş. Gör. Cem BAĞLUM</t>
   </si>
   <si>
+    <t>HIST206</t>
+  </si>
+  <si>
+    <t>B410</t>
+  </si>
+  <si>
+    <t>HIST2006</t>
+  </si>
+  <si>
+    <t>PSYC104</t>
+  </si>
+  <si>
+    <t>Arş. Gör. Oğuz Kaan BULUT</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Onur YAMANER</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Zeynep KABADAYI KUŞCU</t>
+  </si>
+  <si>
+    <t>PSYC456</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Sevinç Serpil Aytaç</t>
+  </si>
+  <si>
+    <t>PSYC 468</t>
+  </si>
+  <si>
+    <t>PSYC 4068</t>
+  </si>
+  <si>
+    <t>STAT202</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Şahamet Bülbül</t>
+  </si>
+  <si>
+    <t>B411</t>
+  </si>
+  <si>
+    <t>B412</t>
+  </si>
+  <si>
+    <t>PSYC1012</t>
+  </si>
+  <si>
+    <t>PSYC 3006</t>
+  </si>
+  <si>
+    <t>PSYC356</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Gökçe Özkılıçcı</t>
+  </si>
+  <si>
+    <t>PSYC364</t>
+  </si>
+  <si>
+    <t>PSYC458</t>
+  </si>
+  <si>
+    <t>PSYC1006</t>
+  </si>
+  <si>
+    <t>PSYC112</t>
+  </si>
+  <si>
+    <t>Dr. Ebru Pehlivan</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Petek Akman Özdemir</t>
+  </si>
+  <si>
+    <t>PSYC204</t>
+  </si>
+  <si>
+    <t>PSYC2004</t>
+  </si>
+  <si>
+    <t>PSYC202</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Birsen ÖZALP</t>
+  </si>
+  <si>
+    <t>PSYC4052</t>
+  </si>
+  <si>
+    <t>PSYC108</t>
+  </si>
+  <si>
+    <t>PSYC2002</t>
+  </si>
+  <si>
+    <t>PSYC302</t>
+  </si>
+  <si>
+    <t>Doç. Dr. Nihan Akıncılar KÖSEOĞLU</t>
+  </si>
+  <si>
+    <t>PSYC 3002</t>
+  </si>
+  <si>
+    <t>PSYC206</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Kübra ÇELİK</t>
+  </si>
+  <si>
+    <t>PSYC2006</t>
+  </si>
+  <si>
+    <t>PSYC460</t>
+  </si>
+  <si>
+    <t>PSYC4060</t>
+  </si>
+  <si>
+    <t>PSYC1008</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Ferhat KUTLU</t>
+  </si>
+  <si>
+    <t>PSYC4002</t>
+  </si>
+  <si>
+    <t>B413</t>
+  </si>
+  <si>
+    <t>PSYC402</t>
+  </si>
+  <si>
+    <t>PSYC304</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Onur Yamaner</t>
+  </si>
+  <si>
     <t>Dr. Öğr. Üyesi Bilge ÇAĞATAY</t>
   </si>
   <si>
-    <t>HIST206</t>
-  </si>
-  <si>
-    <t>B410</t>
-  </si>
-  <si>
-    <t>HIST2006</t>
-  </si>
-  <si>
-    <t>PSYC104</t>
-  </si>
-  <si>
-    <t>Arş. Gör. Oğuz Kaan BULUT</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Onur YAMANER</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Zeynep KABADAYI KUŞCU</t>
-  </si>
-  <si>
-    <t>PSYC456</t>
-  </si>
-  <si>
-    <t>Prof. Dr. Sevinç Serpil Aytaç</t>
-  </si>
-  <si>
-    <t>PSYC 468</t>
-  </si>
-  <si>
-    <t>PSYC 4068</t>
-  </si>
-  <si>
-    <t>STAT202</t>
-  </si>
-  <si>
-    <t>Prof. Dr. Şahamet Bülbül</t>
-  </si>
-  <si>
-    <t>B411</t>
-  </si>
-  <si>
-    <t>B412</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Melike KARATAY</t>
-  </si>
-  <si>
-    <t>PSYC1012</t>
-  </si>
-  <si>
-    <t>PSYC 3006</t>
-  </si>
-  <si>
-    <t>PSYC356</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Gökçe Özkılıçcı</t>
-  </si>
-  <si>
-    <t>PSYC364</t>
-  </si>
-  <si>
-    <t>PSYC458</t>
-  </si>
-  <si>
-    <t>PSYC1006</t>
-  </si>
-  <si>
-    <t>PSYC112</t>
-  </si>
-  <si>
-    <t>Dr. Ebru Pehlivan</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Petek Akman Özdemir</t>
-  </si>
-  <si>
-    <t>PSYC204</t>
-  </si>
-  <si>
-    <t>PSYC2004</t>
-  </si>
-  <si>
-    <t>PSYC202</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Birsen ÖZALP</t>
-  </si>
-  <si>
-    <t>PSYC4052</t>
-  </si>
-  <si>
-    <t>PSYC108</t>
-  </si>
-  <si>
-    <t>PSYC2002</t>
-  </si>
-  <si>
-    <t>PSYC302</t>
-  </si>
-  <si>
-    <t>Doç. Dr. Nihan Akıncılar KÖSEOĞLU</t>
-  </si>
-  <si>
-    <t>PSYC 3002</t>
-  </si>
-  <si>
-    <t>PSYC206</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Kübra ÇELİK</t>
-  </si>
-  <si>
-    <t>PSYC2006</t>
-  </si>
-  <si>
-    <t>PSYC460</t>
-  </si>
-  <si>
-    <t>PSYC4060</t>
-  </si>
-  <si>
-    <t>PSYC1008</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Ferhat KUTLU</t>
-  </si>
-  <si>
-    <t>PSYC4002</t>
-  </si>
-  <si>
-    <t>B413</t>
-  </si>
-  <si>
-    <t>PSYC402</t>
-  </si>
-  <si>
-    <t>PSYC304</t>
-  </si>
-  <si>
     <t>STAT204</t>
   </si>
   <si>
@@ -1568,9 +1568,6 @@
   </si>
   <si>
     <t>Dr. Öğr. Üyesi Ceren İlkay SOYLU KÜÇÜKGÖNCÜ</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Hazar ALTINBAŞ</t>
   </si>
   <si>
     <t>PSYC358</t>
@@ -3634,6 +3631,72 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="27" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="38" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="39" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="39" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="39" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="39" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="39" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="39" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="25" fillId="8" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3834,72 +3897,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="38" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="39" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="39" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="39" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="39" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="39" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="39" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="25" fillId="8" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -4311,10 +4308,10 @@
       <c r="G2" s="41">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H2" s="416" t="s">
+      <c r="H2" s="440" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="416" t="s">
+      <c r="I2" s="440" t="s">
         <v>15</v>
       </c>
       <c r="J2" s="451" t="s">
@@ -4346,8 +4343,8 @@
       <c r="G3" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H3" s="412"/>
-      <c r="I3" s="412"/>
+      <c r="H3" s="436"/>
+      <c r="I3" s="436"/>
       <c r="J3" s="451"/>
       <c r="K3" s="451"/>
     </row>
@@ -4373,8 +4370,8 @@
       <c r="G4" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H4" s="412"/>
-      <c r="I4" s="412"/>
+      <c r="H4" s="436"/>
+      <c r="I4" s="436"/>
       <c r="J4" s="451"/>
       <c r="K4" s="451"/>
     </row>
@@ -4400,8 +4397,8 @@
       <c r="G5" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H5" s="412"/>
-      <c r="I5" s="412"/>
+      <c r="H5" s="436"/>
+      <c r="I5" s="436"/>
       <c r="J5" s="451"/>
       <c r="K5" s="451"/>
     </row>
@@ -4427,8 +4424,8 @@
       <c r="G6" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H6" s="412"/>
-      <c r="I6" s="412"/>
+      <c r="H6" s="436"/>
+      <c r="I6" s="436"/>
       <c r="J6" s="451"/>
       <c r="K6" s="451"/>
     </row>
@@ -4454,8 +4451,8 @@
       <c r="G7" s="48">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H7" s="417"/>
-      <c r="I7" s="417"/>
+      <c r="H7" s="441"/>
+      <c r="I7" s="441"/>
       <c r="J7" s="452"/>
       <c r="K7" s="452"/>
     </row>
@@ -4481,10 +4478,10 @@
       <c r="G8" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H8" s="411" t="s">
+      <c r="H8" s="435" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="411" t="s">
+      <c r="I8" s="435" t="s">
         <v>24</v>
       </c>
       <c r="J8" s="451" t="s">
@@ -4514,8 +4511,8 @@
       <c r="G9" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H9" s="412"/>
-      <c r="I9" s="412"/>
+      <c r="H9" s="436"/>
+      <c r="I9" s="436"/>
       <c r="J9" s="451"/>
       <c r="K9" s="15"/>
     </row>
@@ -4541,8 +4538,8 @@
       <c r="G10" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H10" s="412"/>
-      <c r="I10" s="412"/>
+      <c r="H10" s="436"/>
+      <c r="I10" s="436"/>
       <c r="J10" s="451"/>
       <c r="K10" s="15"/>
     </row>
@@ -4568,8 +4565,8 @@
       <c r="G11" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H11" s="412"/>
-      <c r="I11" s="412"/>
+      <c r="H11" s="436"/>
+      <c r="I11" s="436"/>
       <c r="J11" s="451"/>
       <c r="K11" s="15"/>
     </row>
@@ -4595,8 +4592,8 @@
       <c r="G12" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H12" s="412"/>
-      <c r="I12" s="412"/>
+      <c r="H12" s="436"/>
+      <c r="I12" s="436"/>
       <c r="J12" s="451"/>
       <c r="K12" s="15"/>
     </row>
@@ -4622,8 +4619,8 @@
       <c r="G13" s="51">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H13" s="413"/>
-      <c r="I13" s="413"/>
+      <c r="H13" s="437"/>
+      <c r="I13" s="437"/>
       <c r="J13" s="452"/>
       <c r="K13" s="15"/>
     </row>
@@ -4649,10 +4646,10 @@
       <c r="G14" s="41">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H14" s="411" t="s">
+      <c r="H14" s="435" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="411" t="s">
+      <c r="I14" s="435" t="s">
         <v>27</v>
       </c>
       <c r="J14" s="451" t="s">
@@ -4684,8 +4681,8 @@
       <c r="G15" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H15" s="412"/>
-      <c r="I15" s="412"/>
+      <c r="H15" s="436"/>
+      <c r="I15" s="436"/>
       <c r="J15" s="451"/>
       <c r="K15" s="451"/>
     </row>
@@ -4711,8 +4708,8 @@
       <c r="G16" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H16" s="412"/>
-      <c r="I16" s="412"/>
+      <c r="H16" s="436"/>
+      <c r="I16" s="436"/>
       <c r="J16" s="451"/>
       <c r="K16" s="451"/>
     </row>
@@ -4738,8 +4735,8 @@
       <c r="G17" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H17" s="412"/>
-      <c r="I17" s="412"/>
+      <c r="H17" s="436"/>
+      <c r="I17" s="436"/>
       <c r="J17" s="451"/>
       <c r="K17" s="451"/>
     </row>
@@ -4765,8 +4762,8 @@
       <c r="G18" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H18" s="412"/>
-      <c r="I18" s="412"/>
+      <c r="H18" s="436"/>
+      <c r="I18" s="436"/>
       <c r="J18" s="451"/>
       <c r="K18" s="451"/>
     </row>
@@ -4792,8 +4789,8 @@
       <c r="G19" s="51">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H19" s="413"/>
-      <c r="I19" s="413"/>
+      <c r="H19" s="437"/>
+      <c r="I19" s="437"/>
       <c r="J19" s="452"/>
       <c r="K19" s="452"/>
     </row>
@@ -4819,10 +4816,10 @@
       <c r="G20" s="41">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H20" s="411" t="s">
+      <c r="H20" s="435" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="411" t="s">
+      <c r="I20" s="435" t="s">
         <v>30</v>
       </c>
       <c r="J20" s="451" t="s">
@@ -4854,8 +4851,8 @@
       <c r="G21" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H21" s="412"/>
-      <c r="I21" s="412"/>
+      <c r="H21" s="436"/>
+      <c r="I21" s="436"/>
       <c r="J21" s="451"/>
       <c r="K21" s="451"/>
     </row>
@@ -4881,8 +4878,8 @@
       <c r="G22" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H22" s="412"/>
-      <c r="I22" s="412"/>
+      <c r="H22" s="436"/>
+      <c r="I22" s="436"/>
       <c r="J22" s="451"/>
       <c r="K22" s="451"/>
     </row>
@@ -4908,8 +4905,8 @@
       <c r="G23" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H23" s="412"/>
-      <c r="I23" s="412"/>
+      <c r="H23" s="436"/>
+      <c r="I23" s="436"/>
       <c r="J23" s="451"/>
       <c r="K23" s="451"/>
     </row>
@@ -4935,8 +4932,8 @@
       <c r="G24" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H24" s="412"/>
-      <c r="I24" s="412"/>
+      <c r="H24" s="436"/>
+      <c r="I24" s="436"/>
       <c r="J24" s="451"/>
       <c r="K24" s="451"/>
     </row>
@@ -4962,8 +4959,8 @@
       <c r="G25" s="51">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H25" s="413"/>
-      <c r="I25" s="413"/>
+      <c r="H25" s="437"/>
+      <c r="I25" s="437"/>
       <c r="J25" s="452"/>
       <c r="K25" s="452"/>
     </row>
@@ -4989,10 +4986,10 @@
       <c r="G26" s="41">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H26" s="411" t="s">
+      <c r="H26" s="435" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="411" t="s">
+      <c r="I26" s="435" t="s">
         <v>33</v>
       </c>
       <c r="J26" s="451" t="s">
@@ -5024,8 +5021,8 @@
       <c r="G27" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H27" s="412"/>
-      <c r="I27" s="412"/>
+      <c r="H27" s="436"/>
+      <c r="I27" s="436"/>
       <c r="J27" s="451"/>
       <c r="K27" s="451"/>
     </row>
@@ -5051,8 +5048,8 @@
       <c r="G28" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H28" s="412"/>
-      <c r="I28" s="412"/>
+      <c r="H28" s="436"/>
+      <c r="I28" s="436"/>
       <c r="J28" s="451"/>
       <c r="K28" s="451"/>
     </row>
@@ -5078,8 +5075,8 @@
       <c r="G29" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H29" s="412"/>
-      <c r="I29" s="412"/>
+      <c r="H29" s="436"/>
+      <c r="I29" s="436"/>
       <c r="J29" s="451"/>
       <c r="K29" s="451"/>
     </row>
@@ -5105,8 +5102,8 @@
       <c r="G30" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H30" s="412"/>
-      <c r="I30" s="412"/>
+      <c r="H30" s="436"/>
+      <c r="I30" s="436"/>
       <c r="J30" s="451"/>
       <c r="K30" s="451"/>
     </row>
@@ -5132,8 +5129,8 @@
       <c r="G31" s="51">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H31" s="413"/>
-      <c r="I31" s="413"/>
+      <c r="H31" s="437"/>
+      <c r="I31" s="437"/>
       <c r="J31" s="452"/>
       <c r="K31" s="452"/>
     </row>
@@ -5159,10 +5156,10 @@
       <c r="G32" s="41">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H32" s="411" t="s">
+      <c r="H32" s="435" t="s">
         <v>35</v>
       </c>
-      <c r="I32" s="411" t="s">
+      <c r="I32" s="435" t="s">
         <v>36</v>
       </c>
       <c r="J32" s="451" t="s">
@@ -5194,8 +5191,8 @@
       <c r="G33" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H33" s="412"/>
-      <c r="I33" s="412"/>
+      <c r="H33" s="436"/>
+      <c r="I33" s="436"/>
       <c r="J33" s="451"/>
       <c r="K33" s="451"/>
     </row>
@@ -5221,8 +5218,8 @@
       <c r="G34" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H34" s="412"/>
-      <c r="I34" s="412"/>
+      <c r="H34" s="436"/>
+      <c r="I34" s="436"/>
       <c r="J34" s="451"/>
       <c r="K34" s="451"/>
     </row>
@@ -5248,8 +5245,8 @@
       <c r="G35" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H35" s="412"/>
-      <c r="I35" s="412"/>
+      <c r="H35" s="436"/>
+      <c r="I35" s="436"/>
       <c r="J35" s="451"/>
       <c r="K35" s="451"/>
     </row>
@@ -5275,8 +5272,8 @@
       <c r="G36" s="45">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H36" s="412"/>
-      <c r="I36" s="412"/>
+      <c r="H36" s="436"/>
+      <c r="I36" s="436"/>
       <c r="J36" s="451"/>
       <c r="K36" s="451"/>
     </row>
@@ -5302,8 +5299,8 @@
       <c r="G37" s="51">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H37" s="413"/>
-      <c r="I37" s="413"/>
+      <c r="H37" s="437"/>
+      <c r="I37" s="437"/>
       <c r="J37" s="452"/>
       <c r="K37" s="452"/>
     </row>
@@ -5329,10 +5326,10 @@
       <c r="G38" s="6">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H38" s="374" t="s">
+      <c r="H38" s="398" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="374" t="s">
+      <c r="I38" s="398" t="s">
         <v>15</v>
       </c>
       <c r="J38" s="453" t="s">
@@ -5364,8 +5361,8 @@
       <c r="G39" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H39" s="366"/>
-      <c r="I39" s="366"/>
+      <c r="H39" s="390"/>
+      <c r="I39" s="390"/>
       <c r="J39" s="454"/>
       <c r="K39" s="454"/>
     </row>
@@ -5391,8 +5388,8 @@
       <c r="G40" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H40" s="366"/>
-      <c r="I40" s="366"/>
+      <c r="H40" s="390"/>
+      <c r="I40" s="390"/>
       <c r="J40" s="454"/>
       <c r="K40" s="454"/>
     </row>
@@ -5418,8 +5415,8 @@
       <c r="G41" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H41" s="366"/>
-      <c r="I41" s="366"/>
+      <c r="H41" s="390"/>
+      <c r="I41" s="390"/>
       <c r="J41" s="454"/>
       <c r="K41" s="454"/>
     </row>
@@ -5445,8 +5442,8 @@
       <c r="G42" s="14">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H42" s="367"/>
-      <c r="I42" s="367"/>
+      <c r="H42" s="391"/>
+      <c r="I42" s="391"/>
       <c r="J42" s="455"/>
       <c r="K42" s="454"/>
     </row>
@@ -5472,10 +5469,10 @@
       <c r="G43" s="6">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H43" s="365" t="s">
+      <c r="H43" s="389" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="365" t="s">
+      <c r="I43" s="389" t="s">
         <v>24</v>
       </c>
       <c r="J43" s="453" t="s">
@@ -5505,8 +5502,8 @@
       <c r="G44" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H44" s="366"/>
-      <c r="I44" s="366"/>
+      <c r="H44" s="390"/>
+      <c r="I44" s="390"/>
       <c r="J44" s="454"/>
       <c r="K44" s="15"/>
     </row>
@@ -5532,8 +5529,8 @@
       <c r="G45" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H45" s="366"/>
-      <c r="I45" s="366"/>
+      <c r="H45" s="390"/>
+      <c r="I45" s="390"/>
       <c r="J45" s="454"/>
       <c r="K45" s="15"/>
     </row>
@@ -5559,8 +5556,8 @@
       <c r="G46" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H46" s="366"/>
-      <c r="I46" s="366"/>
+      <c r="H46" s="390"/>
+      <c r="I46" s="390"/>
       <c r="J46" s="454"/>
       <c r="K46" s="15"/>
     </row>
@@ -5586,8 +5583,8 @@
       <c r="G47" s="14">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H47" s="375"/>
-      <c r="I47" s="375"/>
+      <c r="H47" s="399"/>
+      <c r="I47" s="399"/>
       <c r="J47" s="454"/>
       <c r="K47" s="15"/>
     </row>
@@ -5613,10 +5610,10 @@
       <c r="G48" s="6">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H48" s="365" t="s">
+      <c r="H48" s="389" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="365" t="s">
+      <c r="I48" s="389" t="s">
         <v>27</v>
       </c>
       <c r="J48" s="453" t="s">
@@ -5648,8 +5645,8 @@
       <c r="G49" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H49" s="366"/>
-      <c r="I49" s="366"/>
+      <c r="H49" s="390"/>
+      <c r="I49" s="390"/>
       <c r="J49" s="454"/>
       <c r="K49" s="454"/>
     </row>
@@ -5675,8 +5672,8 @@
       <c r="G50" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H50" s="366"/>
-      <c r="I50" s="366"/>
+      <c r="H50" s="390"/>
+      <c r="I50" s="390"/>
       <c r="J50" s="454"/>
       <c r="K50" s="454"/>
     </row>
@@ -5702,8 +5699,8 @@
       <c r="G51" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H51" s="366"/>
-      <c r="I51" s="366"/>
+      <c r="H51" s="390"/>
+      <c r="I51" s="390"/>
       <c r="J51" s="454"/>
       <c r="K51" s="454"/>
     </row>
@@ -5729,8 +5726,8 @@
       <c r="G52" s="14">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H52" s="375"/>
-      <c r="I52" s="375"/>
+      <c r="H52" s="399"/>
+      <c r="I52" s="399"/>
       <c r="J52" s="454"/>
       <c r="K52" s="454"/>
     </row>
@@ -5756,10 +5753,10 @@
       <c r="G53" s="6">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H53" s="365" t="s">
+      <c r="H53" s="389" t="s">
         <v>29</v>
       </c>
-      <c r="I53" s="365" t="s">
+      <c r="I53" s="389" t="s">
         <v>30</v>
       </c>
       <c r="J53" s="453" t="s">
@@ -5791,8 +5788,8 @@
       <c r="G54" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H54" s="366"/>
-      <c r="I54" s="366"/>
+      <c r="H54" s="390"/>
+      <c r="I54" s="390"/>
       <c r="J54" s="454"/>
       <c r="K54" s="454"/>
     </row>
@@ -5818,8 +5815,8 @@
       <c r="G55" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H55" s="366"/>
-      <c r="I55" s="366"/>
+      <c r="H55" s="390"/>
+      <c r="I55" s="390"/>
       <c r="J55" s="454"/>
       <c r="K55" s="454"/>
     </row>
@@ -5845,8 +5842,8 @@
       <c r="G56" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H56" s="366"/>
-      <c r="I56" s="366"/>
+      <c r="H56" s="390"/>
+      <c r="I56" s="390"/>
       <c r="J56" s="454"/>
       <c r="K56" s="454"/>
     </row>
@@ -5872,8 +5869,8 @@
       <c r="G57" s="14">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H57" s="375"/>
-      <c r="I57" s="375"/>
+      <c r="H57" s="399"/>
+      <c r="I57" s="399"/>
       <c r="J57" s="454"/>
       <c r="K57" s="454"/>
     </row>
@@ -5899,10 +5896,10 @@
       <c r="G58" s="6">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H58" s="365" t="s">
+      <c r="H58" s="389" t="s">
         <v>32</v>
       </c>
-      <c r="I58" s="365" t="s">
+      <c r="I58" s="389" t="s">
         <v>33</v>
       </c>
       <c r="J58" s="453" t="s">
@@ -5934,8 +5931,8 @@
       <c r="G59" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H59" s="366"/>
-      <c r="I59" s="366"/>
+      <c r="H59" s="390"/>
+      <c r="I59" s="390"/>
       <c r="J59" s="454"/>
       <c r="K59" s="454"/>
     </row>
@@ -5961,8 +5958,8 @@
       <c r="G60" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H60" s="366"/>
-      <c r="I60" s="366"/>
+      <c r="H60" s="390"/>
+      <c r="I60" s="390"/>
       <c r="J60" s="454"/>
       <c r="K60" s="454"/>
     </row>
@@ -5988,8 +5985,8 @@
       <c r="G61" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H61" s="366"/>
-      <c r="I61" s="366"/>
+      <c r="H61" s="390"/>
+      <c r="I61" s="390"/>
       <c r="J61" s="454"/>
       <c r="K61" s="454"/>
     </row>
@@ -6015,8 +6012,8 @@
       <c r="G62" s="14">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H62" s="375"/>
-      <c r="I62" s="375"/>
+      <c r="H62" s="399"/>
+      <c r="I62" s="399"/>
       <c r="J62" s="454"/>
       <c r="K62" s="454"/>
     </row>
@@ -6042,10 +6039,10 @@
       <c r="G63" s="6">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H63" s="365" t="s">
+      <c r="H63" s="389" t="s">
         <v>35</v>
       </c>
-      <c r="I63" s="365" t="s">
+      <c r="I63" s="389" t="s">
         <v>36</v>
       </c>
       <c r="J63" s="453" t="s">
@@ -6077,8 +6074,8 @@
       <c r="G64" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H64" s="366"/>
-      <c r="I64" s="366"/>
+      <c r="H64" s="390"/>
+      <c r="I64" s="390"/>
       <c r="J64" s="454"/>
       <c r="K64" s="454"/>
     </row>
@@ -6104,8 +6101,8 @@
       <c r="G65" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H65" s="366"/>
-      <c r="I65" s="366"/>
+      <c r="H65" s="390"/>
+      <c r="I65" s="390"/>
       <c r="J65" s="454"/>
       <c r="K65" s="454"/>
     </row>
@@ -6131,8 +6128,8 @@
       <c r="G66" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H66" s="366"/>
-      <c r="I66" s="366"/>
+      <c r="H66" s="390"/>
+      <c r="I66" s="390"/>
       <c r="J66" s="454"/>
       <c r="K66" s="454"/>
     </row>
@@ -6158,8 +6155,8 @@
       <c r="G67" s="14">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H67" s="375"/>
-      <c r="I67" s="375"/>
+      <c r="H67" s="399"/>
+      <c r="I67" s="399"/>
       <c r="J67" s="454"/>
       <c r="K67" s="454"/>
     </row>
@@ -6185,10 +6182,10 @@
       <c r="G68" s="6">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H68" s="407" t="s">
+      <c r="H68" s="431" t="s">
         <v>39</v>
       </c>
-      <c r="I68" s="407" t="s">
+      <c r="I68" s="431" t="s">
         <v>40</v>
       </c>
       <c r="J68" s="453" t="s">
@@ -6220,8 +6217,8 @@
       <c r="G69" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H69" s="408"/>
-      <c r="I69" s="408"/>
+      <c r="H69" s="432"/>
+      <c r="I69" s="432"/>
       <c r="J69" s="454"/>
       <c r="K69" s="454"/>
     </row>
@@ -6247,8 +6244,8 @@
       <c r="G70" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H70" s="408"/>
-      <c r="I70" s="408"/>
+      <c r="H70" s="432"/>
+      <c r="I70" s="432"/>
       <c r="J70" s="454"/>
       <c r="K70" s="454"/>
     </row>
@@ -6274,8 +6271,8 @@
       <c r="G71" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H71" s="408"/>
-      <c r="I71" s="408"/>
+      <c r="H71" s="432"/>
+      <c r="I71" s="432"/>
       <c r="J71" s="454"/>
       <c r="K71" s="454"/>
     </row>
@@ -6301,8 +6298,8 @@
       <c r="G72" s="14">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H72" s="415"/>
-      <c r="I72" s="415"/>
+      <c r="H72" s="439"/>
+      <c r="I72" s="439"/>
       <c r="J72" s="454"/>
       <c r="K72" s="454"/>
     </row>
@@ -6328,10 +6325,10 @@
       <c r="G73" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H73" s="381" t="s">
+      <c r="H73" s="405" t="s">
         <v>41</v>
       </c>
-      <c r="I73" s="381" t="s">
+      <c r="I73" s="405" t="s">
         <v>42</v>
       </c>
       <c r="J73" s="456" t="s">
@@ -6363,8 +6360,8 @@
       <c r="G74" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H74" s="394"/>
-      <c r="I74" s="394"/>
+      <c r="H74" s="418"/>
+      <c r="I74" s="418"/>
       <c r="J74" s="457"/>
       <c r="K74" s="457"/>
     </row>
@@ -6390,8 +6387,8 @@
       <c r="G75" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H75" s="394"/>
-      <c r="I75" s="394"/>
+      <c r="H75" s="418"/>
+      <c r="I75" s="418"/>
       <c r="J75" s="457"/>
       <c r="K75" s="457"/>
     </row>
@@ -6417,8 +6414,8 @@
       <c r="G76" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H76" s="394"/>
-      <c r="I76" s="394"/>
+      <c r="H76" s="418"/>
+      <c r="I76" s="418"/>
       <c r="J76" s="457"/>
       <c r="K76" s="457"/>
     </row>
@@ -6444,8 +6441,8 @@
       <c r="G77" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H77" s="382"/>
-      <c r="I77" s="382"/>
+      <c r="H77" s="406"/>
+      <c r="I77" s="406"/>
       <c r="J77" s="457"/>
       <c r="K77" s="457"/>
     </row>
@@ -6471,10 +6468,10 @@
       <c r="G78" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H78" s="381" t="s">
+      <c r="H78" s="405" t="s">
         <v>35</v>
       </c>
-      <c r="I78" s="381" t="s">
+      <c r="I78" s="405" t="s">
         <v>36</v>
       </c>
       <c r="J78" s="456" t="s">
@@ -6504,8 +6501,8 @@
       <c r="G79" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H79" s="394"/>
-      <c r="I79" s="394"/>
+      <c r="H79" s="418"/>
+      <c r="I79" s="418"/>
       <c r="J79" s="457"/>
       <c r="K79" s="15"/>
     </row>
@@ -6531,8 +6528,8 @@
       <c r="G80" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H80" s="394"/>
-      <c r="I80" s="394"/>
+      <c r="H80" s="418"/>
+      <c r="I80" s="418"/>
       <c r="J80" s="457"/>
       <c r="K80" s="15"/>
     </row>
@@ -6558,8 +6555,8 @@
       <c r="G81" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H81" s="394"/>
-      <c r="I81" s="394"/>
+      <c r="H81" s="418"/>
+      <c r="I81" s="418"/>
       <c r="J81" s="457"/>
       <c r="K81" s="15"/>
     </row>
@@ -6585,8 +6582,8 @@
       <c r="G82" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H82" s="382"/>
-      <c r="I82" s="382"/>
+      <c r="H82" s="406"/>
+      <c r="I82" s="406"/>
       <c r="J82" s="457"/>
       <c r="K82" s="15"/>
     </row>
@@ -6612,10 +6609,10 @@
       <c r="G83" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H83" s="381" t="s">
+      <c r="H83" s="405" t="s">
         <v>43</v>
       </c>
-      <c r="I83" s="381" t="s">
+      <c r="I83" s="405" t="s">
         <v>44</v>
       </c>
       <c r="J83" s="456" t="s">
@@ -6647,8 +6644,8 @@
       <c r="G84" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H84" s="394"/>
-      <c r="I84" s="394"/>
+      <c r="H84" s="418"/>
+      <c r="I84" s="418"/>
       <c r="J84" s="457"/>
       <c r="K84" s="457"/>
     </row>
@@ -6674,8 +6671,8 @@
       <c r="G85" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H85" s="394"/>
-      <c r="I85" s="394"/>
+      <c r="H85" s="418"/>
+      <c r="I85" s="418"/>
       <c r="J85" s="457"/>
       <c r="K85" s="457"/>
     </row>
@@ -6701,8 +6698,8 @@
       <c r="G86" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H86" s="394"/>
-      <c r="I86" s="394"/>
+      <c r="H86" s="418"/>
+      <c r="I86" s="418"/>
       <c r="J86" s="457"/>
       <c r="K86" s="457"/>
     </row>
@@ -6728,8 +6725,8 @@
       <c r="G87" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H87" s="382"/>
-      <c r="I87" s="382"/>
+      <c r="H87" s="406"/>
+      <c r="I87" s="406"/>
       <c r="J87" s="457"/>
       <c r="K87" s="457"/>
     </row>
@@ -6755,10 +6752,10 @@
       <c r="G88" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H88" s="381" t="s">
+      <c r="H88" s="405" t="s">
         <v>45</v>
       </c>
-      <c r="I88" s="381" t="s">
+      <c r="I88" s="405" t="s">
         <v>46</v>
       </c>
       <c r="J88" s="456" t="s">
@@ -6790,8 +6787,8 @@
       <c r="G89" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H89" s="394"/>
-      <c r="I89" s="394"/>
+      <c r="H89" s="418"/>
+      <c r="I89" s="418"/>
       <c r="J89" s="457"/>
       <c r="K89" s="457"/>
     </row>
@@ -6817,8 +6814,8 @@
       <c r="G90" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H90" s="394"/>
-      <c r="I90" s="394"/>
+      <c r="H90" s="418"/>
+      <c r="I90" s="418"/>
       <c r="J90" s="457"/>
       <c r="K90" s="457"/>
     </row>
@@ -6844,8 +6841,8 @@
       <c r="G91" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H91" s="394"/>
-      <c r="I91" s="394"/>
+      <c r="H91" s="418"/>
+      <c r="I91" s="418"/>
       <c r="J91" s="457"/>
       <c r="K91" s="457"/>
     </row>
@@ -6871,8 +6868,8 @@
       <c r="G92" s="26">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H92" s="382"/>
-      <c r="I92" s="382"/>
+      <c r="H92" s="406"/>
+      <c r="I92" s="406"/>
       <c r="J92" s="457"/>
       <c r="K92" s="457"/>
     </row>
@@ -6898,10 +6895,10 @@
       <c r="G93" s="27">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H93" s="381" t="s">
+      <c r="H93" s="405" t="s">
         <v>47</v>
       </c>
-      <c r="I93" s="381" t="s">
+      <c r="I93" s="405" t="s">
         <v>48</v>
       </c>
       <c r="J93" s="456" t="s">
@@ -6933,8 +6930,8 @@
       <c r="G94" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H94" s="394"/>
-      <c r="I94" s="394"/>
+      <c r="H94" s="418"/>
+      <c r="I94" s="418"/>
       <c r="J94" s="457"/>
       <c r="K94" s="457"/>
     </row>
@@ -6960,8 +6957,8 @@
       <c r="G95" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H95" s="394"/>
-      <c r="I95" s="394"/>
+      <c r="H95" s="418"/>
+      <c r="I95" s="418"/>
       <c r="J95" s="457"/>
       <c r="K95" s="457"/>
     </row>
@@ -6987,8 +6984,8 @@
       <c r="G96" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H96" s="394"/>
-      <c r="I96" s="394"/>
+      <c r="H96" s="418"/>
+      <c r="I96" s="418"/>
       <c r="J96" s="457"/>
       <c r="K96" s="457"/>
     </row>
@@ -7014,8 +7011,8 @@
       <c r="G97" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H97" s="382"/>
-      <c r="I97" s="382"/>
+      <c r="H97" s="406"/>
+      <c r="I97" s="406"/>
       <c r="J97" s="457"/>
       <c r="K97" s="457"/>
     </row>
@@ -7041,10 +7038,10 @@
       <c r="G98" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H98" s="381" t="s">
+      <c r="H98" s="405" t="s">
         <v>49</v>
       </c>
-      <c r="I98" s="381" t="s">
+      <c r="I98" s="405" t="s">
         <v>50</v>
       </c>
       <c r="J98" s="456" t="s">
@@ -7076,8 +7073,8 @@
       <c r="G99" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H99" s="394"/>
-      <c r="I99" s="394"/>
+      <c r="H99" s="418"/>
+      <c r="I99" s="418"/>
       <c r="J99" s="457"/>
       <c r="K99" s="457"/>
     </row>
@@ -7103,8 +7100,8 @@
       <c r="G100" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H100" s="394"/>
-      <c r="I100" s="394"/>
+      <c r="H100" s="418"/>
+      <c r="I100" s="418"/>
       <c r="J100" s="457"/>
       <c r="K100" s="457"/>
     </row>
@@ -7130,8 +7127,8 @@
       <c r="G101" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H101" s="394"/>
-      <c r="I101" s="394"/>
+      <c r="H101" s="418"/>
+      <c r="I101" s="418"/>
       <c r="J101" s="457"/>
       <c r="K101" s="457"/>
     </row>
@@ -7157,8 +7154,8 @@
       <c r="G102" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H102" s="382"/>
-      <c r="I102" s="382"/>
+      <c r="H102" s="406"/>
+      <c r="I102" s="406"/>
       <c r="J102" s="457"/>
       <c r="K102" s="457"/>
     </row>
@@ -7184,10 +7181,10 @@
       <c r="G103" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H103" s="418" t="s">
+      <c r="H103" s="442" t="s">
         <v>51</v>
       </c>
-      <c r="I103" s="418" t="s">
+      <c r="I103" s="442" t="s">
         <v>52</v>
       </c>
       <c r="J103" s="456" t="s">
@@ -7219,8 +7216,8 @@
       <c r="G104" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H104" s="419"/>
-      <c r="I104" s="419"/>
+      <c r="H104" s="443"/>
+      <c r="I104" s="443"/>
       <c r="J104" s="457"/>
       <c r="K104" s="457"/>
     </row>
@@ -7246,8 +7243,8 @@
       <c r="G105" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H105" s="419"/>
-      <c r="I105" s="419"/>
+      <c r="H105" s="443"/>
+      <c r="I105" s="443"/>
       <c r="J105" s="457"/>
       <c r="K105" s="457"/>
     </row>
@@ -7273,8 +7270,8 @@
       <c r="G106" s="19">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H106" s="419"/>
-      <c r="I106" s="419"/>
+      <c r="H106" s="443"/>
+      <c r="I106" s="443"/>
       <c r="J106" s="457"/>
       <c r="K106" s="457"/>
     </row>
@@ -7300,8 +7297,8 @@
       <c r="G107" s="23">
         <v>0.61805555555555558</v>
       </c>
-      <c r="H107" s="420"/>
-      <c r="I107" s="420"/>
+      <c r="H107" s="444"/>
+      <c r="I107" s="444"/>
       <c r="J107" s="457"/>
       <c r="K107" s="457"/>
     </row>
@@ -7327,10 +7324,10 @@
       <c r="G108" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H108" s="404" t="s">
+      <c r="H108" s="428" t="s">
         <v>53</v>
       </c>
-      <c r="I108" s="404" t="s">
+      <c r="I108" s="428" t="s">
         <v>42</v>
       </c>
       <c r="J108" s="458" t="s">
@@ -7362,8 +7359,8 @@
       <c r="G109" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H109" s="405"/>
-      <c r="I109" s="405"/>
+      <c r="H109" s="429"/>
+      <c r="I109" s="429"/>
       <c r="J109" s="459"/>
       <c r="K109" s="459"/>
     </row>
@@ -7389,8 +7386,8 @@
       <c r="G110" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H110" s="405"/>
-      <c r="I110" s="405"/>
+      <c r="H110" s="429"/>
+      <c r="I110" s="429"/>
       <c r="J110" s="459"/>
       <c r="K110" s="459"/>
     </row>
@@ -7416,8 +7413,8 @@
       <c r="G111" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H111" s="405"/>
-      <c r="I111" s="405"/>
+      <c r="H111" s="429"/>
+      <c r="I111" s="429"/>
       <c r="J111" s="459"/>
       <c r="K111" s="459"/>
     </row>
@@ -7443,8 +7440,8 @@
       <c r="G112" s="37">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H112" s="406"/>
-      <c r="I112" s="406"/>
+      <c r="H112" s="430"/>
+      <c r="I112" s="430"/>
       <c r="J112" s="460"/>
       <c r="K112" s="460"/>
     </row>
@@ -7470,10 +7467,10 @@
       <c r="G113" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H113" s="404" t="s">
+      <c r="H113" s="428" t="s">
         <v>35</v>
       </c>
-      <c r="I113" s="404" t="s">
+      <c r="I113" s="428" t="s">
         <v>36</v>
       </c>
       <c r="J113" s="458" t="s">
@@ -7503,8 +7500,8 @@
       <c r="G114" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H114" s="405"/>
-      <c r="I114" s="405"/>
+      <c r="H114" s="429"/>
+      <c r="I114" s="429"/>
       <c r="J114" s="459"/>
       <c r="K114" s="15"/>
     </row>
@@ -7530,8 +7527,8 @@
       <c r="G115" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H115" s="405"/>
-      <c r="I115" s="405"/>
+      <c r="H115" s="429"/>
+      <c r="I115" s="429"/>
       <c r="J115" s="459"/>
       <c r="K115" s="15"/>
     </row>
@@ -7557,8 +7554,8 @@
       <c r="G116" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H116" s="405"/>
-      <c r="I116" s="405"/>
+      <c r="H116" s="429"/>
+      <c r="I116" s="429"/>
       <c r="J116" s="459"/>
       <c r="K116" s="15"/>
     </row>
@@ -7584,8 +7581,8 @@
       <c r="G117" s="37">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H117" s="406"/>
-      <c r="I117" s="406"/>
+      <c r="H117" s="430"/>
+      <c r="I117" s="430"/>
       <c r="J117" s="460"/>
       <c r="K117" s="15"/>
     </row>
@@ -7611,10 +7608,10 @@
       <c r="G118" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H118" s="404" t="s">
+      <c r="H118" s="428" t="s">
         <v>43</v>
       </c>
-      <c r="I118" s="404" t="s">
+      <c r="I118" s="428" t="s">
         <v>44</v>
       </c>
       <c r="J118" s="458" t="s">
@@ -7646,8 +7643,8 @@
       <c r="G119" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H119" s="405"/>
-      <c r="I119" s="405"/>
+      <c r="H119" s="429"/>
+      <c r="I119" s="429"/>
       <c r="J119" s="459"/>
       <c r="K119" s="459"/>
     </row>
@@ -7673,8 +7670,8 @@
       <c r="G120" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H120" s="405"/>
-      <c r="I120" s="405"/>
+      <c r="H120" s="429"/>
+      <c r="I120" s="429"/>
       <c r="J120" s="459"/>
       <c r="K120" s="459"/>
     </row>
@@ -7700,8 +7697,8 @@
       <c r="G121" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H121" s="405"/>
-      <c r="I121" s="405"/>
+      <c r="H121" s="429"/>
+      <c r="I121" s="429"/>
       <c r="J121" s="459"/>
       <c r="K121" s="459"/>
     </row>
@@ -7727,8 +7724,8 @@
       <c r="G122" s="37">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H122" s="406"/>
-      <c r="I122" s="406"/>
+      <c r="H122" s="430"/>
+      <c r="I122" s="430"/>
       <c r="J122" s="460"/>
       <c r="K122" s="460"/>
     </row>
@@ -7754,10 +7751,10 @@
       <c r="G123" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H123" s="404" t="s">
+      <c r="H123" s="428" t="s">
         <v>45</v>
       </c>
-      <c r="I123" s="404" t="s">
+      <c r="I123" s="428" t="s">
         <v>46</v>
       </c>
       <c r="J123" s="458" t="s">
@@ -7789,8 +7786,8 @@
       <c r="G124" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H124" s="405"/>
-      <c r="I124" s="405"/>
+      <c r="H124" s="429"/>
+      <c r="I124" s="429"/>
       <c r="J124" s="459"/>
       <c r="K124" s="459"/>
     </row>
@@ -7816,8 +7813,8 @@
       <c r="G125" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H125" s="405"/>
-      <c r="I125" s="405"/>
+      <c r="H125" s="429"/>
+      <c r="I125" s="429"/>
       <c r="J125" s="459"/>
       <c r="K125" s="459"/>
     </row>
@@ -7843,8 +7840,8 @@
       <c r="G126" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H126" s="405"/>
-      <c r="I126" s="405"/>
+      <c r="H126" s="429"/>
+      <c r="I126" s="429"/>
       <c r="J126" s="459"/>
       <c r="K126" s="459"/>
     </row>
@@ -7870,8 +7867,8 @@
       <c r="G127" s="37">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H127" s="406"/>
-      <c r="I127" s="406"/>
+      <c r="H127" s="430"/>
+      <c r="I127" s="430"/>
       <c r="J127" s="460"/>
       <c r="K127" s="460"/>
     </row>
@@ -7897,10 +7894,10 @@
       <c r="G128" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H128" s="404" t="s">
+      <c r="H128" s="428" t="s">
         <v>47</v>
       </c>
-      <c r="I128" s="404" t="s">
+      <c r="I128" s="428" t="s">
         <v>48</v>
       </c>
       <c r="J128" s="458" t="s">
@@ -7932,8 +7929,8 @@
       <c r="G129" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H129" s="405"/>
-      <c r="I129" s="405"/>
+      <c r="H129" s="429"/>
+      <c r="I129" s="429"/>
       <c r="J129" s="459"/>
       <c r="K129" s="459"/>
     </row>
@@ -7959,8 +7956,8 @@
       <c r="G130" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H130" s="405"/>
-      <c r="I130" s="405"/>
+      <c r="H130" s="429"/>
+      <c r="I130" s="429"/>
       <c r="J130" s="459"/>
       <c r="K130" s="459"/>
     </row>
@@ -7986,8 +7983,8 @@
       <c r="G131" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H131" s="405"/>
-      <c r="I131" s="405"/>
+      <c r="H131" s="429"/>
+      <c r="I131" s="429"/>
       <c r="J131" s="459"/>
       <c r="K131" s="459"/>
     </row>
@@ -8013,8 +8010,8 @@
       <c r="G132" s="37">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H132" s="406"/>
-      <c r="I132" s="406"/>
+      <c r="H132" s="430"/>
+      <c r="I132" s="430"/>
       <c r="J132" s="460"/>
       <c r="K132" s="460"/>
     </row>
@@ -8040,10 +8037,10 @@
       <c r="G133" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H133" s="404" t="s">
+      <c r="H133" s="428" t="s">
         <v>49</v>
       </c>
-      <c r="I133" s="404" t="s">
+      <c r="I133" s="428" t="s">
         <v>50</v>
       </c>
       <c r="J133" s="458" t="s">
@@ -8075,8 +8072,8 @@
       <c r="G134" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H134" s="405"/>
-      <c r="I134" s="405"/>
+      <c r="H134" s="429"/>
+      <c r="I134" s="429"/>
       <c r="J134" s="459"/>
       <c r="K134" s="459"/>
     </row>
@@ -8102,8 +8099,8 @@
       <c r="G135" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H135" s="405"/>
-      <c r="I135" s="405"/>
+      <c r="H135" s="429"/>
+      <c r="I135" s="429"/>
       <c r="J135" s="459"/>
       <c r="K135" s="459"/>
     </row>
@@ -8129,8 +8126,8 @@
       <c r="G136" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H136" s="405"/>
-      <c r="I136" s="405"/>
+      <c r="H136" s="429"/>
+      <c r="I136" s="429"/>
       <c r="J136" s="459"/>
       <c r="K136" s="459"/>
     </row>
@@ -8156,8 +8153,8 @@
       <c r="G137" s="37">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H137" s="406"/>
-      <c r="I137" s="406"/>
+      <c r="H137" s="430"/>
+      <c r="I137" s="430"/>
       <c r="J137" s="460"/>
       <c r="K137" s="460"/>
     </row>
@@ -8183,10 +8180,10 @@
       <c r="G138" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H138" s="396" t="s">
+      <c r="H138" s="420" t="s">
         <v>51</v>
       </c>
-      <c r="I138" s="396" t="s">
+      <c r="I138" s="420" t="s">
         <v>52</v>
       </c>
       <c r="J138" s="458" t="s">
@@ -8218,8 +8215,8 @@
       <c r="G139" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H139" s="397"/>
-      <c r="I139" s="397"/>
+      <c r="H139" s="421"/>
+      <c r="I139" s="421"/>
       <c r="J139" s="459"/>
       <c r="K139" s="459"/>
     </row>
@@ -8245,8 +8242,8 @@
       <c r="G140" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H140" s="397"/>
-      <c r="I140" s="397"/>
+      <c r="H140" s="421"/>
+      <c r="I140" s="421"/>
       <c r="J140" s="459"/>
       <c r="K140" s="459"/>
     </row>
@@ -8272,8 +8269,8 @@
       <c r="G141" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H141" s="397"/>
-      <c r="I141" s="397"/>
+      <c r="H141" s="421"/>
+      <c r="I141" s="421"/>
       <c r="J141" s="459"/>
       <c r="K141" s="459"/>
     </row>
@@ -8299,8 +8296,8 @@
       <c r="G142" s="37">
         <v>0.70138888888888884</v>
       </c>
-      <c r="H142" s="414"/>
-      <c r="I142" s="414"/>
+      <c r="H142" s="438"/>
+      <c r="I142" s="438"/>
       <c r="J142" s="460"/>
       <c r="K142" s="460"/>
     </row>
@@ -8326,16 +8323,16 @@
       <c r="G143" s="182">
         <v>0.75</v>
       </c>
-      <c r="H143" s="381" t="s">
+      <c r="H143" s="405" t="s">
         <v>54</v>
       </c>
-      <c r="I143" s="381" t="s">
+      <c r="I143" s="405" t="s">
         <v>55</v>
       </c>
-      <c r="J143" s="391" t="s">
+      <c r="J143" s="415" t="s">
         <v>16</v>
       </c>
-      <c r="K143" s="391" t="s">
+      <c r="K143" s="415" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8361,10 +8358,10 @@
       <c r="G144" s="185">
         <v>0.75</v>
       </c>
-      <c r="H144" s="394"/>
-      <c r="I144" s="394"/>
-      <c r="J144" s="392"/>
-      <c r="K144" s="392"/>
+      <c r="H144" s="418"/>
+      <c r="I144" s="418"/>
+      <c r="J144" s="416"/>
+      <c r="K144" s="416"/>
     </row>
     <row r="145" spans="1:11" ht="15.75">
       <c r="A145" s="186" t="s">
@@ -8388,10 +8385,10 @@
       <c r="G145" s="188">
         <v>0.75</v>
       </c>
-      <c r="H145" s="382"/>
-      <c r="I145" s="382"/>
-      <c r="J145" s="393"/>
-      <c r="K145" s="393"/>
+      <c r="H145" s="406"/>
+      <c r="I145" s="406"/>
+      <c r="J145" s="417"/>
+      <c r="K145" s="417"/>
     </row>
     <row r="146" spans="1:11" ht="15.75">
       <c r="A146" s="180" t="s">
@@ -8415,13 +8412,13 @@
       <c r="G146" s="182">
         <v>0.75</v>
       </c>
-      <c r="H146" s="381" t="s">
+      <c r="H146" s="405" t="s">
         <v>56</v>
       </c>
-      <c r="I146" s="381" t="s">
+      <c r="I146" s="405" t="s">
         <v>57</v>
       </c>
-      <c r="J146" s="391" t="s">
+      <c r="J146" s="415" t="s">
         <v>16</v>
       </c>
       <c r="K146" s="15"/>
@@ -8448,9 +8445,9 @@
       <c r="G147" s="185">
         <v>0.75</v>
       </c>
-      <c r="H147" s="394"/>
-      <c r="I147" s="394"/>
-      <c r="J147" s="392"/>
+      <c r="H147" s="418"/>
+      <c r="I147" s="418"/>
+      <c r="J147" s="416"/>
       <c r="K147" s="15"/>
     </row>
     <row r="148" spans="1:11" ht="15.75">
@@ -8475,9 +8472,9 @@
       <c r="G148" s="191">
         <v>0.75</v>
       </c>
-      <c r="H148" s="382"/>
-      <c r="I148" s="382"/>
-      <c r="J148" s="393"/>
+      <c r="H148" s="406"/>
+      <c r="I148" s="406"/>
+      <c r="J148" s="417"/>
       <c r="K148" s="15"/>
     </row>
     <row r="149" spans="1:11" ht="15.75">
@@ -8502,16 +8499,16 @@
       <c r="G149" s="185">
         <v>0.75</v>
       </c>
-      <c r="H149" s="381" t="s">
+      <c r="H149" s="405" t="s">
         <v>58</v>
       </c>
-      <c r="I149" s="381" t="s">
+      <c r="I149" s="405" t="s">
         <v>59</v>
       </c>
-      <c r="J149" s="391" t="s">
+      <c r="J149" s="415" t="s">
         <v>16</v>
       </c>
-      <c r="K149" s="391" t="s">
+      <c r="K149" s="415" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8537,10 +8534,10 @@
       <c r="G150" s="185">
         <v>0.75</v>
       </c>
-      <c r="H150" s="394"/>
-      <c r="I150" s="394"/>
-      <c r="J150" s="392"/>
-      <c r="K150" s="392"/>
+      <c r="H150" s="418"/>
+      <c r="I150" s="418"/>
+      <c r="J150" s="416"/>
+      <c r="K150" s="416"/>
     </row>
     <row r="151" spans="1:11" ht="15.75">
       <c r="A151" s="186" t="s">
@@ -8564,10 +8561,10 @@
       <c r="G151" s="188">
         <v>0.75</v>
       </c>
-      <c r="H151" s="382"/>
-      <c r="I151" s="382"/>
-      <c r="J151" s="393"/>
-      <c r="K151" s="393"/>
+      <c r="H151" s="406"/>
+      <c r="I151" s="406"/>
+      <c r="J151" s="417"/>
+      <c r="K151" s="417"/>
     </row>
     <row r="152" spans="1:11" ht="15.75">
       <c r="A152" s="4" t="s">
@@ -8591,16 +8588,16 @@
       <c r="G152" s="6">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H152" s="365" t="s">
+      <c r="H152" s="389" t="s">
         <v>60</v>
       </c>
-      <c r="I152" s="365" t="s">
+      <c r="I152" s="389" t="s">
         <v>61</v>
       </c>
-      <c r="J152" s="362" t="s">
+      <c r="J152" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="K152" s="362" t="s">
+      <c r="K152" s="386" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8626,10 +8623,10 @@
       <c r="G153" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H153" s="366"/>
-      <c r="I153" s="366"/>
-      <c r="J153" s="363"/>
-      <c r="K153" s="363"/>
+      <c r="H153" s="390"/>
+      <c r="I153" s="390"/>
+      <c r="J153" s="387"/>
+      <c r="K153" s="387"/>
     </row>
     <row r="154" spans="1:11" ht="15.75">
       <c r="A154" s="7" t="s">
@@ -8653,10 +8650,10 @@
       <c r="G154" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H154" s="366"/>
-      <c r="I154" s="366"/>
-      <c r="J154" s="363"/>
-      <c r="K154" s="363"/>
+      <c r="H154" s="390"/>
+      <c r="I154" s="390"/>
+      <c r="J154" s="387"/>
+      <c r="K154" s="387"/>
     </row>
     <row r="155" spans="1:11" ht="15.75">
       <c r="A155" s="12" t="s">
@@ -8680,10 +8677,10 @@
       <c r="G155" s="14">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H155" s="367"/>
-      <c r="I155" s="367"/>
-      <c r="J155" s="364"/>
-      <c r="K155" s="364"/>
+      <c r="H155" s="391"/>
+      <c r="I155" s="391"/>
+      <c r="J155" s="388"/>
+      <c r="K155" s="388"/>
     </row>
     <row r="156" spans="1:11" ht="15.75">
       <c r="A156" s="4" t="s">
@@ -8707,13 +8704,13 @@
       <c r="G156" s="6">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H156" s="365" t="s">
+      <c r="H156" s="389" t="s">
         <v>62</v>
       </c>
-      <c r="I156" s="365" t="s">
+      <c r="I156" s="389" t="s">
         <v>63</v>
       </c>
-      <c r="J156" s="362" t="s">
+      <c r="J156" s="386" t="s">
         <v>16</v>
       </c>
       <c r="K156" s="15"/>
@@ -8740,9 +8737,9 @@
       <c r="G157" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H157" s="366"/>
-      <c r="I157" s="366"/>
-      <c r="J157" s="363"/>
+      <c r="H157" s="390"/>
+      <c r="I157" s="390"/>
+      <c r="J157" s="387"/>
       <c r="K157" s="15"/>
     </row>
     <row r="158" spans="1:11" ht="15.75">
@@ -8767,9 +8764,9 @@
       <c r="G158" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H158" s="366"/>
-      <c r="I158" s="366"/>
-      <c r="J158" s="363"/>
+      <c r="H158" s="390"/>
+      <c r="I158" s="390"/>
+      <c r="J158" s="387"/>
       <c r="K158" s="15"/>
     </row>
     <row r="159" spans="1:11" ht="15.75">
@@ -8794,9 +8791,9 @@
       <c r="G159" s="54">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H159" s="367"/>
-      <c r="I159" s="367"/>
-      <c r="J159" s="364"/>
+      <c r="H159" s="391"/>
+      <c r="I159" s="391"/>
+      <c r="J159" s="388"/>
       <c r="K159" s="15"/>
     </row>
     <row r="160" spans="1:11" ht="15.75">
@@ -8821,16 +8818,16 @@
       <c r="G160" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H160" s="365" t="s">
+      <c r="H160" s="389" t="s">
         <v>64</v>
       </c>
-      <c r="I160" s="365" t="s">
+      <c r="I160" s="389" t="s">
         <v>65</v>
       </c>
-      <c r="J160" s="362" t="s">
+      <c r="J160" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="K160" s="362" t="s">
+      <c r="K160" s="386" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8856,10 +8853,10 @@
       <c r="G161" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H161" s="366"/>
-      <c r="I161" s="366"/>
-      <c r="J161" s="363"/>
-      <c r="K161" s="363"/>
+      <c r="H161" s="390"/>
+      <c r="I161" s="390"/>
+      <c r="J161" s="387"/>
+      <c r="K161" s="387"/>
     </row>
     <row r="162" spans="1:11" ht="15.75">
       <c r="A162" s="7" t="s">
@@ -8883,10 +8880,10 @@
       <c r="G162" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H162" s="366"/>
-      <c r="I162" s="366"/>
-      <c r="J162" s="363"/>
-      <c r="K162" s="363"/>
+      <c r="H162" s="390"/>
+      <c r="I162" s="390"/>
+      <c r="J162" s="387"/>
+      <c r="K162" s="387"/>
     </row>
     <row r="163" spans="1:11" ht="15.75">
       <c r="A163" s="52" t="s">
@@ -8910,10 +8907,10 @@
       <c r="G163" s="54">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H163" s="367"/>
-      <c r="I163" s="367"/>
-      <c r="J163" s="364"/>
-      <c r="K163" s="364"/>
+      <c r="H163" s="391"/>
+      <c r="I163" s="391"/>
+      <c r="J163" s="388"/>
+      <c r="K163" s="388"/>
     </row>
     <row r="164" spans="1:11" ht="15.75">
       <c r="A164" s="7" t="s">
@@ -8937,16 +8934,16 @@
       <c r="G164" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H164" s="368" t="s">
+      <c r="H164" s="392" t="s">
         <v>43</v>
       </c>
-      <c r="I164" s="371" t="s">
+      <c r="I164" s="395" t="s">
         <v>44</v>
       </c>
-      <c r="J164" s="362" t="s">
+      <c r="J164" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="K164" s="362" t="s">
+      <c r="K164" s="386" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8972,10 +8969,10 @@
       <c r="G165" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H165" s="369"/>
-      <c r="I165" s="372"/>
-      <c r="J165" s="363"/>
-      <c r="K165" s="363"/>
+      <c r="H165" s="393"/>
+      <c r="I165" s="396"/>
+      <c r="J165" s="387"/>
+      <c r="K165" s="387"/>
     </row>
     <row r="166" spans="1:11" ht="15.75">
       <c r="A166" s="7" t="s">
@@ -8999,10 +8996,10 @@
       <c r="G166" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H166" s="369"/>
-      <c r="I166" s="372"/>
-      <c r="J166" s="363"/>
-      <c r="K166" s="363"/>
+      <c r="H166" s="393"/>
+      <c r="I166" s="396"/>
+      <c r="J166" s="387"/>
+      <c r="K166" s="387"/>
     </row>
     <row r="167" spans="1:11" ht="15.75">
       <c r="A167" s="12" t="s">
@@ -9026,10 +9023,10 @@
       <c r="G167" s="14">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H167" s="370"/>
-      <c r="I167" s="373"/>
-      <c r="J167" s="364"/>
-      <c r="K167" s="364"/>
+      <c r="H167" s="394"/>
+      <c r="I167" s="397"/>
+      <c r="J167" s="388"/>
+      <c r="K167" s="388"/>
     </row>
     <row r="168" spans="1:11" ht="15.75">
       <c r="A168" s="4" t="s">
@@ -9053,16 +9050,16 @@
       <c r="G168" s="6">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H168" s="368" t="s">
+      <c r="H168" s="392" t="s">
         <v>66</v>
       </c>
-      <c r="I168" s="371" t="s">
+      <c r="I168" s="395" t="s">
         <v>67</v>
       </c>
-      <c r="J168" s="362" t="s">
+      <c r="J168" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="K168" s="362" t="s">
+      <c r="K168" s="386" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9088,10 +9085,10 @@
       <c r="G169" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H169" s="369"/>
-      <c r="I169" s="372"/>
-      <c r="J169" s="363"/>
-      <c r="K169" s="363"/>
+      <c r="H169" s="393"/>
+      <c r="I169" s="396"/>
+      <c r="J169" s="387"/>
+      <c r="K169" s="387"/>
     </row>
     <row r="170" spans="1:11" ht="15.75">
       <c r="A170" s="7" t="s">
@@ -9115,10 +9112,10 @@
       <c r="G170" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H170" s="369"/>
-      <c r="I170" s="372"/>
-      <c r="J170" s="363"/>
-      <c r="K170" s="363"/>
+      <c r="H170" s="393"/>
+      <c r="I170" s="396"/>
+      <c r="J170" s="387"/>
+      <c r="K170" s="387"/>
     </row>
     <row r="171" spans="1:11" ht="15.75">
       <c r="A171" s="52" t="s">
@@ -9142,10 +9139,10 @@
       <c r="G171" s="54">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H171" s="370"/>
-      <c r="I171" s="373"/>
-      <c r="J171" s="364"/>
-      <c r="K171" s="364"/>
+      <c r="H171" s="394"/>
+      <c r="I171" s="397"/>
+      <c r="J171" s="388"/>
+      <c r="K171" s="388"/>
     </row>
     <row r="172" spans="1:11" ht="15.75">
       <c r="A172" s="7" t="s">
@@ -9169,16 +9166,16 @@
       <c r="G172" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H172" s="365" t="s">
+      <c r="H172" s="389" t="s">
         <v>49</v>
       </c>
-      <c r="I172" s="365" t="s">
+      <c r="I172" s="389" t="s">
         <v>50</v>
       </c>
-      <c r="J172" s="362" t="s">
+      <c r="J172" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="K172" s="362" t="s">
+      <c r="K172" s="386" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9204,10 +9201,10 @@
       <c r="G173" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H173" s="366"/>
-      <c r="I173" s="366"/>
-      <c r="J173" s="363"/>
-      <c r="K173" s="363"/>
+      <c r="H173" s="390"/>
+      <c r="I173" s="390"/>
+      <c r="J173" s="387"/>
+      <c r="K173" s="387"/>
     </row>
     <row r="174" spans="1:11" ht="15.75">
       <c r="A174" s="7" t="s">
@@ -9231,10 +9228,10 @@
       <c r="G174" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H174" s="366"/>
-      <c r="I174" s="366"/>
-      <c r="J174" s="363"/>
-      <c r="K174" s="363"/>
+      <c r="H174" s="390"/>
+      <c r="I174" s="390"/>
+      <c r="J174" s="387"/>
+      <c r="K174" s="387"/>
     </row>
     <row r="175" spans="1:11" ht="15.75">
       <c r="A175" s="12" t="s">
@@ -9258,10 +9255,10 @@
       <c r="G175" s="14">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H175" s="367"/>
-      <c r="I175" s="367"/>
-      <c r="J175" s="364"/>
-      <c r="K175" s="364"/>
+      <c r="H175" s="391"/>
+      <c r="I175" s="391"/>
+      <c r="J175" s="388"/>
+      <c r="K175" s="388"/>
     </row>
     <row r="176" spans="1:11" ht="15.75">
       <c r="A176" s="4" t="s">
@@ -9285,16 +9282,16 @@
       <c r="G176" s="6">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H176" s="407" t="s">
+      <c r="H176" s="431" t="s">
         <v>68</v>
       </c>
-      <c r="I176" s="407" t="s">
+      <c r="I176" s="431" t="s">
         <v>53</v>
       </c>
-      <c r="J176" s="362" t="s">
+      <c r="J176" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="K176" s="362" t="s">
+      <c r="K176" s="386" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9320,10 +9317,10 @@
       <c r="G177" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H177" s="408"/>
-      <c r="I177" s="408"/>
-      <c r="J177" s="363"/>
-      <c r="K177" s="363"/>
+      <c r="H177" s="432"/>
+      <c r="I177" s="432"/>
+      <c r="J177" s="387"/>
+      <c r="K177" s="387"/>
     </row>
     <row r="178" spans="1:11" ht="15.75">
       <c r="A178" s="7" t="s">
@@ -9347,10 +9344,10 @@
       <c r="G178" s="11">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H178" s="408"/>
-      <c r="I178" s="408"/>
-      <c r="J178" s="363"/>
-      <c r="K178" s="363"/>
+      <c r="H178" s="432"/>
+      <c r="I178" s="432"/>
+      <c r="J178" s="387"/>
+      <c r="K178" s="387"/>
     </row>
     <row r="179" spans="1:11" ht="15.75">
       <c r="A179" s="12" t="s">
@@ -9374,10 +9371,10 @@
       <c r="G179" s="14">
         <v>0.4513888888888889</v>
       </c>
-      <c r="H179" s="408"/>
-      <c r="I179" s="408"/>
-      <c r="J179" s="364"/>
-      <c r="K179" s="364"/>
+      <c r="H179" s="432"/>
+      <c r="I179" s="432"/>
+      <c r="J179" s="388"/>
+      <c r="K179" s="388"/>
     </row>
     <row r="180" spans="1:11" ht="15.75">
       <c r="A180" s="55" t="s">
@@ -9401,10 +9398,10 @@
       <c r="G180" s="57">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H180" s="409" t="s">
+      <c r="H180" s="433" t="s">
         <v>60</v>
       </c>
-      <c r="I180" s="410" t="s">
+      <c r="I180" s="434" t="s">
         <v>61</v>
       </c>
       <c r="J180" s="461" t="s">
@@ -9436,8 +9433,8 @@
       <c r="G181" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H181" s="399"/>
-      <c r="I181" s="402"/>
+      <c r="H181" s="423"/>
+      <c r="I181" s="426"/>
       <c r="J181" s="462"/>
       <c r="K181" s="462"/>
     </row>
@@ -9463,8 +9460,8 @@
       <c r="G182" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H182" s="399"/>
-      <c r="I182" s="402"/>
+      <c r="H182" s="423"/>
+      <c r="I182" s="426"/>
       <c r="J182" s="462"/>
       <c r="K182" s="462"/>
     </row>
@@ -9490,8 +9487,8 @@
       <c r="G183" s="63">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H183" s="400"/>
-      <c r="I183" s="403"/>
+      <c r="H183" s="424"/>
+      <c r="I183" s="427"/>
       <c r="J183" s="463"/>
       <c r="K183" s="463"/>
     </row>
@@ -9517,10 +9514,10 @@
       <c r="G184" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H184" s="398" t="s">
+      <c r="H184" s="422" t="s">
         <v>62</v>
       </c>
-      <c r="I184" s="404" t="s">
+      <c r="I184" s="428" t="s">
         <v>63</v>
       </c>
       <c r="J184" s="461" t="s">
@@ -9550,8 +9547,8 @@
       <c r="G185" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H185" s="399"/>
-      <c r="I185" s="405"/>
+      <c r="H185" s="423"/>
+      <c r="I185" s="429"/>
       <c r="J185" s="462"/>
       <c r="K185" s="64"/>
     </row>
@@ -9577,8 +9574,8 @@
       <c r="G186" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H186" s="399"/>
-      <c r="I186" s="405"/>
+      <c r="H186" s="423"/>
+      <c r="I186" s="429"/>
       <c r="J186" s="462"/>
       <c r="K186" s="64"/>
     </row>
@@ -9604,8 +9601,8 @@
       <c r="G187" s="67">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H187" s="400"/>
-      <c r="I187" s="406"/>
+      <c r="H187" s="424"/>
+      <c r="I187" s="430"/>
       <c r="J187" s="463"/>
       <c r="K187" s="64"/>
     </row>
@@ -9631,10 +9628,10 @@
       <c r="G188" s="57">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H188" s="398" t="s">
+      <c r="H188" s="422" t="s">
         <v>64</v>
       </c>
-      <c r="I188" s="401" t="s">
+      <c r="I188" s="425" t="s">
         <v>65</v>
       </c>
       <c r="J188" s="461" t="s">
@@ -9666,8 +9663,8 @@
       <c r="G189" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H189" s="399"/>
-      <c r="I189" s="402"/>
+      <c r="H189" s="423"/>
+      <c r="I189" s="426"/>
       <c r="J189" s="462"/>
       <c r="K189" s="462"/>
     </row>
@@ -9693,8 +9690,8 @@
       <c r="G190" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H190" s="399"/>
-      <c r="I190" s="402"/>
+      <c r="H190" s="423"/>
+      <c r="I190" s="426"/>
       <c r="J190" s="462"/>
       <c r="K190" s="462"/>
     </row>
@@ -9720,8 +9717,8 @@
       <c r="G191" s="67">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H191" s="400"/>
-      <c r="I191" s="403"/>
+      <c r="H191" s="424"/>
+      <c r="I191" s="427"/>
       <c r="J191" s="463"/>
       <c r="K191" s="463"/>
     </row>
@@ -9747,10 +9744,10 @@
       <c r="G192" s="57">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H192" s="398" t="s">
+      <c r="H192" s="422" t="s">
         <v>43</v>
       </c>
-      <c r="I192" s="401" t="s">
+      <c r="I192" s="425" t="s">
         <v>44</v>
       </c>
       <c r="J192" s="461" t="s">
@@ -9782,8 +9779,8 @@
       <c r="G193" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H193" s="399"/>
-      <c r="I193" s="402"/>
+      <c r="H193" s="423"/>
+      <c r="I193" s="426"/>
       <c r="J193" s="462"/>
       <c r="K193" s="462"/>
     </row>
@@ -9809,8 +9806,8 @@
       <c r="G194" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H194" s="399"/>
-      <c r="I194" s="402"/>
+      <c r="H194" s="423"/>
+      <c r="I194" s="426"/>
       <c r="J194" s="462"/>
       <c r="K194" s="462"/>
     </row>
@@ -9836,8 +9833,8 @@
       <c r="G195" s="67">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H195" s="400"/>
-      <c r="I195" s="403"/>
+      <c r="H195" s="424"/>
+      <c r="I195" s="427"/>
       <c r="J195" s="463"/>
       <c r="K195" s="463"/>
     </row>
@@ -9863,10 +9860,10 @@
       <c r="G196" s="57">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H196" s="398" t="s">
+      <c r="H196" s="422" t="s">
         <v>66</v>
       </c>
-      <c r="I196" s="401" t="s">
+      <c r="I196" s="425" t="s">
         <v>67</v>
       </c>
       <c r="J196" s="461" t="s">
@@ -9898,8 +9895,8 @@
       <c r="G197" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H197" s="399"/>
-      <c r="I197" s="402"/>
+      <c r="H197" s="423"/>
+      <c r="I197" s="426"/>
       <c r="J197" s="462"/>
       <c r="K197" s="462"/>
     </row>
@@ -9925,8 +9922,8 @@
       <c r="G198" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H198" s="399"/>
-      <c r="I198" s="402"/>
+      <c r="H198" s="423"/>
+      <c r="I198" s="426"/>
       <c r="J198" s="462"/>
       <c r="K198" s="462"/>
     </row>
@@ -9952,8 +9949,8 @@
       <c r="G199" s="63">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H199" s="400"/>
-      <c r="I199" s="403"/>
+      <c r="H199" s="424"/>
+      <c r="I199" s="427"/>
       <c r="J199" s="463"/>
       <c r="K199" s="463"/>
     </row>
@@ -9979,10 +9976,10 @@
       <c r="G200" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H200" s="396" t="s">
+      <c r="H200" s="420" t="s">
         <v>68</v>
       </c>
-      <c r="I200" s="396" t="s">
+      <c r="I200" s="420" t="s">
         <v>53</v>
       </c>
       <c r="J200" s="461" t="s">
@@ -10014,8 +10011,8 @@
       <c r="G201" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H201" s="397"/>
-      <c r="I201" s="397"/>
+      <c r="H201" s="421"/>
+      <c r="I201" s="421"/>
       <c r="J201" s="462"/>
       <c r="K201" s="462"/>
     </row>
@@ -10041,8 +10038,8 @@
       <c r="G202" s="60">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H202" s="397"/>
-      <c r="I202" s="397"/>
+      <c r="H202" s="421"/>
+      <c r="I202" s="421"/>
       <c r="J202" s="462"/>
       <c r="K202" s="462"/>
     </row>
@@ -10068,8 +10065,8 @@
       <c r="G203" s="67">
         <v>0.53472222222222221</v>
       </c>
-      <c r="H203" s="397"/>
-      <c r="I203" s="397"/>
+      <c r="H203" s="421"/>
+      <c r="I203" s="421"/>
       <c r="J203" s="463"/>
       <c r="K203" s="463"/>
     </row>
@@ -10095,10 +10092,10 @@
       <c r="G204" s="19">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H204" s="384" t="s">
+      <c r="H204" s="408" t="s">
         <v>14</v>
       </c>
-      <c r="I204" s="384" t="s">
+      <c r="I204" s="408" t="s">
         <v>15</v>
       </c>
       <c r="J204" s="464" t="s">
@@ -10130,8 +10127,8 @@
       <c r="G205" s="82">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H205" s="382"/>
-      <c r="I205" s="382"/>
+      <c r="H205" s="406"/>
+      <c r="I205" s="406"/>
       <c r="J205" s="465"/>
       <c r="K205" s="465"/>
     </row>
@@ -10157,10 +10154,10 @@
       <c r="G206" s="27">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H206" s="384" t="s">
+      <c r="H206" s="408" t="s">
         <v>64</v>
       </c>
-      <c r="I206" s="384" t="s">
+      <c r="I206" s="408" t="s">
         <v>65</v>
       </c>
       <c r="J206" s="464" t="s">
@@ -10190,8 +10187,8 @@
       <c r="G207" s="82">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H207" s="382"/>
-      <c r="I207" s="382"/>
+      <c r="H207" s="406"/>
+      <c r="I207" s="406"/>
       <c r="J207" s="465"/>
       <c r="K207" s="15"/>
     </row>
@@ -10217,10 +10214,10 @@
       <c r="G208" s="27">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H208" s="384" t="s">
+      <c r="H208" s="408" t="s">
         <v>26</v>
       </c>
-      <c r="I208" s="384" t="s">
+      <c r="I208" s="408" t="s">
         <v>27</v>
       </c>
       <c r="J208" s="464" t="s">
@@ -10252,8 +10249,8 @@
       <c r="G209" s="82">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H209" s="382"/>
-      <c r="I209" s="382"/>
+      <c r="H209" s="406"/>
+      <c r="I209" s="406"/>
       <c r="J209" s="465"/>
       <c r="K209" s="465"/>
     </row>
@@ -10279,10 +10276,10 @@
       <c r="G210" s="27">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H210" s="384" t="s">
+      <c r="H210" s="408" t="s">
         <v>29</v>
       </c>
-      <c r="I210" s="384" t="s">
+      <c r="I210" s="408" t="s">
         <v>30</v>
       </c>
       <c r="J210" s="464" t="s">
@@ -10314,8 +10311,8 @@
       <c r="G211" s="82">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H211" s="382"/>
-      <c r="I211" s="382"/>
+      <c r="H211" s="406"/>
+      <c r="I211" s="406"/>
       <c r="J211" s="465"/>
       <c r="K211" s="465"/>
     </row>
@@ -10341,10 +10338,10 @@
       <c r="G212" s="27">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H212" s="384" t="s">
+      <c r="H212" s="408" t="s">
         <v>66</v>
       </c>
-      <c r="I212" s="384" t="s">
+      <c r="I212" s="408" t="s">
         <v>67</v>
       </c>
       <c r="J212" s="464" t="s">
@@ -10376,8 +10373,8 @@
       <c r="G213" s="84">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H213" s="382"/>
-      <c r="I213" s="382"/>
+      <c r="H213" s="406"/>
+      <c r="I213" s="406"/>
       <c r="J213" s="465"/>
       <c r="K213" s="465"/>
     </row>
@@ -10403,10 +10400,10 @@
       <c r="G214" s="19">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H214" s="381" t="s">
+      <c r="H214" s="405" t="s">
         <v>71</v>
       </c>
-      <c r="I214" s="381" t="s">
+      <c r="I214" s="405" t="s">
         <v>72</v>
       </c>
       <c r="J214" s="464" t="s">
@@ -10438,8 +10435,8 @@
       <c r="G215" s="84">
         <v>0.60416666666666663</v>
       </c>
-      <c r="H215" s="382"/>
-      <c r="I215" s="382"/>
+      <c r="H215" s="406"/>
+      <c r="I215" s="406"/>
       <c r="J215" s="465"/>
       <c r="K215" s="465"/>
     </row>
@@ -10465,10 +10462,10 @@
       <c r="G216" s="70">
         <v>0.6875</v>
       </c>
-      <c r="H216" s="385" t="s">
+      <c r="H216" s="409" t="s">
         <v>14</v>
       </c>
-      <c r="I216" s="388" t="s">
+      <c r="I216" s="412" t="s">
         <v>15</v>
       </c>
       <c r="J216" s="466" t="s">
@@ -10500,8 +10497,8 @@
       <c r="G217" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H217" s="386"/>
-      <c r="I217" s="389"/>
+      <c r="H217" s="410"/>
+      <c r="I217" s="413"/>
       <c r="J217" s="467"/>
       <c r="K217" s="467"/>
     </row>
@@ -10527,8 +10524,8 @@
       <c r="G218" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H218" s="386"/>
-      <c r="I218" s="389"/>
+      <c r="H218" s="410"/>
+      <c r="I218" s="413"/>
       <c r="J218" s="467"/>
       <c r="K218" s="467"/>
     </row>
@@ -10554,8 +10551,8 @@
       <c r="G219" s="77">
         <v>0.6875</v>
       </c>
-      <c r="H219" s="387"/>
-      <c r="I219" s="390"/>
+      <c r="H219" s="411"/>
+      <c r="I219" s="414"/>
       <c r="J219" s="468"/>
       <c r="K219" s="468"/>
     </row>
@@ -10581,10 +10578,10 @@
       <c r="G220" s="70">
         <v>0.6875</v>
       </c>
-      <c r="H220" s="385" t="s">
+      <c r="H220" s="409" t="s">
         <v>64</v>
       </c>
-      <c r="I220" s="388" t="s">
+      <c r="I220" s="412" t="s">
         <v>65</v>
       </c>
       <c r="J220" s="466" t="s">
@@ -10614,8 +10611,8 @@
       <c r="G221" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H221" s="386"/>
-      <c r="I221" s="389"/>
+      <c r="H221" s="410"/>
+      <c r="I221" s="413"/>
       <c r="J221" s="467"/>
       <c r="K221" s="15"/>
     </row>
@@ -10641,8 +10638,8 @@
       <c r="G222" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H222" s="386"/>
-      <c r="I222" s="389"/>
+      <c r="H222" s="410"/>
+      <c r="I222" s="413"/>
       <c r="J222" s="467"/>
       <c r="K222" s="15"/>
     </row>
@@ -10668,8 +10665,8 @@
       <c r="G223" s="77">
         <v>0.6875</v>
       </c>
-      <c r="H223" s="387"/>
-      <c r="I223" s="390"/>
+      <c r="H223" s="411"/>
+      <c r="I223" s="414"/>
       <c r="J223" s="468"/>
       <c r="K223" s="15"/>
     </row>
@@ -10695,10 +10692,10 @@
       <c r="G224" s="70">
         <v>0.6875</v>
       </c>
-      <c r="H224" s="385" t="s">
+      <c r="H224" s="409" t="s">
         <v>26</v>
       </c>
-      <c r="I224" s="388" t="s">
+      <c r="I224" s="412" t="s">
         <v>27</v>
       </c>
       <c r="J224" s="466" t="s">
@@ -10730,8 +10727,8 @@
       <c r="G225" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H225" s="386"/>
-      <c r="I225" s="389"/>
+      <c r="H225" s="410"/>
+      <c r="I225" s="413"/>
       <c r="J225" s="467"/>
       <c r="K225" s="467"/>
     </row>
@@ -10757,8 +10754,8 @@
       <c r="G226" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H226" s="386"/>
-      <c r="I226" s="389"/>
+      <c r="H226" s="410"/>
+      <c r="I226" s="413"/>
       <c r="J226" s="467"/>
       <c r="K226" s="467"/>
     </row>
@@ -10784,8 +10781,8 @@
       <c r="G227" s="80">
         <v>0.6875</v>
       </c>
-      <c r="H227" s="387"/>
-      <c r="I227" s="390"/>
+      <c r="H227" s="411"/>
+      <c r="I227" s="414"/>
       <c r="J227" s="468"/>
       <c r="K227" s="468"/>
     </row>
@@ -10811,10 +10808,10 @@
       <c r="G228" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H228" s="385" t="s">
+      <c r="H228" s="409" t="s">
         <v>29</v>
       </c>
-      <c r="I228" s="388" t="s">
+      <c r="I228" s="412" t="s">
         <v>30</v>
       </c>
       <c r="J228" s="466" t="s">
@@ -10846,8 +10843,8 @@
       <c r="G229" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H229" s="386"/>
-      <c r="I229" s="389"/>
+      <c r="H229" s="410"/>
+      <c r="I229" s="413"/>
       <c r="J229" s="467"/>
       <c r="K229" s="467"/>
     </row>
@@ -10873,8 +10870,8 @@
       <c r="G230" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H230" s="386"/>
-      <c r="I230" s="389"/>
+      <c r="H230" s="410"/>
+      <c r="I230" s="413"/>
       <c r="J230" s="467"/>
       <c r="K230" s="467"/>
     </row>
@@ -10900,8 +10897,8 @@
       <c r="G231" s="80">
         <v>0.6875</v>
       </c>
-      <c r="H231" s="387"/>
-      <c r="I231" s="390"/>
+      <c r="H231" s="411"/>
+      <c r="I231" s="414"/>
       <c r="J231" s="468"/>
       <c r="K231" s="468"/>
     </row>
@@ -10927,10 +10924,10 @@
       <c r="G232" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H232" s="385" t="s">
+      <c r="H232" s="409" t="s">
         <v>66</v>
       </c>
-      <c r="I232" s="388" t="s">
+      <c r="I232" s="412" t="s">
         <v>67</v>
       </c>
       <c r="J232" s="466" t="s">
@@ -10962,8 +10959,8 @@
       <c r="G233" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H233" s="386"/>
-      <c r="I233" s="389"/>
+      <c r="H233" s="410"/>
+      <c r="I233" s="413"/>
       <c r="J233" s="467"/>
       <c r="K233" s="467"/>
     </row>
@@ -10989,8 +10986,8 @@
       <c r="G234" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H234" s="386"/>
-      <c r="I234" s="389"/>
+      <c r="H234" s="410"/>
+      <c r="I234" s="413"/>
       <c r="J234" s="467"/>
       <c r="K234" s="467"/>
     </row>
@@ -11016,8 +11013,8 @@
       <c r="G235" s="80">
         <v>0.6875</v>
       </c>
-      <c r="H235" s="387"/>
-      <c r="I235" s="390"/>
+      <c r="H235" s="411"/>
+      <c r="I235" s="414"/>
       <c r="J235" s="468"/>
       <c r="K235" s="468"/>
     </row>
@@ -11043,10 +11040,10 @@
       <c r="G236" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H236" s="385" t="s">
+      <c r="H236" s="409" t="s">
         <v>71</v>
       </c>
-      <c r="I236" s="388" t="s">
+      <c r="I236" s="412" t="s">
         <v>72</v>
       </c>
       <c r="J236" s="466" t="s">
@@ -11078,8 +11075,8 @@
       <c r="G237" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H237" s="386"/>
-      <c r="I237" s="389"/>
+      <c r="H237" s="410"/>
+      <c r="I237" s="413"/>
       <c r="J237" s="467"/>
       <c r="K237" s="467"/>
     </row>
@@ -11105,8 +11102,8 @@
       <c r="G238" s="74">
         <v>0.6875</v>
       </c>
-      <c r="H238" s="386"/>
-      <c r="I238" s="389"/>
+      <c r="H238" s="410"/>
+      <c r="I238" s="413"/>
       <c r="J238" s="467"/>
       <c r="K238" s="467"/>
     </row>
@@ -11132,8 +11129,8 @@
       <c r="G239" s="77">
         <v>0.6875</v>
       </c>
-      <c r="H239" s="387"/>
-      <c r="I239" s="390"/>
+      <c r="H239" s="411"/>
+      <c r="I239" s="414"/>
       <c r="J239" s="468"/>
       <c r="K239" s="468"/>
     </row>
@@ -11159,10 +11156,10 @@
       <c r="G240" s="87">
         <v>0.75</v>
       </c>
-      <c r="H240" s="383" t="s">
+      <c r="H240" s="407" t="s">
         <v>73</v>
       </c>
-      <c r="I240" s="383" t="s">
+      <c r="I240" s="407" t="s">
         <v>74</v>
       </c>
       <c r="J240" s="469" t="s">
@@ -11194,8 +11191,8 @@
       <c r="G241" s="91">
         <v>0.75</v>
       </c>
-      <c r="H241" s="379"/>
-      <c r="I241" s="379"/>
+      <c r="H241" s="403"/>
+      <c r="I241" s="403"/>
       <c r="J241" s="469"/>
       <c r="K241" s="469"/>
     </row>
@@ -11221,8 +11218,8 @@
       <c r="G242" s="94">
         <v>0.75</v>
       </c>
-      <c r="H242" s="380"/>
-      <c r="I242" s="380"/>
+      <c r="H242" s="404"/>
+      <c r="I242" s="404"/>
       <c r="J242" s="469"/>
       <c r="K242" s="469"/>
     </row>
@@ -11248,10 +11245,10 @@
       <c r="G243" s="87">
         <v>0.75</v>
       </c>
-      <c r="H243" s="378" t="s">
+      <c r="H243" s="402" t="s">
         <v>23</v>
       </c>
-      <c r="I243" s="378" t="s">
+      <c r="I243" s="402" t="s">
         <v>24</v>
       </c>
       <c r="J243" s="470" t="s">
@@ -11281,8 +11278,8 @@
       <c r="G244" s="91">
         <v>0.75</v>
       </c>
-      <c r="H244" s="379"/>
-      <c r="I244" s="379"/>
+      <c r="H244" s="403"/>
+      <c r="I244" s="403"/>
       <c r="J244" s="469"/>
       <c r="K244" s="64"/>
     </row>
@@ -11308,8 +11305,8 @@
       <c r="G245" s="94">
         <v>0.75</v>
       </c>
-      <c r="H245" s="380"/>
-      <c r="I245" s="380"/>
+      <c r="H245" s="404"/>
+      <c r="I245" s="404"/>
       <c r="J245" s="469"/>
       <c r="K245" s="64"/>
     </row>
@@ -11335,10 +11332,10 @@
       <c r="G246" s="87">
         <v>0.75</v>
       </c>
-      <c r="H246" s="378" t="s">
+      <c r="H246" s="402" t="s">
         <v>76</v>
       </c>
-      <c r="I246" s="378" t="s">
+      <c r="I246" s="402" t="s">
         <v>77</v>
       </c>
       <c r="J246" s="470" t="s">
@@ -11370,8 +11367,8 @@
       <c r="G247" s="91">
         <v>0.75</v>
       </c>
-      <c r="H247" s="379"/>
-      <c r="I247" s="379"/>
+      <c r="H247" s="403"/>
+      <c r="I247" s="403"/>
       <c r="J247" s="469"/>
       <c r="K247" s="469"/>
     </row>
@@ -11397,8 +11394,8 @@
       <c r="G248" s="94">
         <v>0.75</v>
       </c>
-      <c r="H248" s="380"/>
-      <c r="I248" s="380"/>
+      <c r="H248" s="404"/>
+      <c r="I248" s="404"/>
       <c r="J248" s="469"/>
       <c r="K248" s="469"/>
     </row>
@@ -11424,10 +11421,10 @@
       <c r="G249" s="87">
         <v>0.75</v>
       </c>
-      <c r="H249" s="378" t="s">
+      <c r="H249" s="402" t="s">
         <v>41</v>
       </c>
-      <c r="I249" s="378" t="s">
+      <c r="I249" s="402" t="s">
         <v>42</v>
       </c>
       <c r="J249" s="470" t="s">
@@ -11459,8 +11456,8 @@
       <c r="G250" s="91">
         <v>0.75</v>
       </c>
-      <c r="H250" s="379"/>
-      <c r="I250" s="379"/>
+      <c r="H250" s="403"/>
+      <c r="I250" s="403"/>
       <c r="J250" s="469"/>
       <c r="K250" s="469"/>
     </row>
@@ -11486,8 +11483,8 @@
       <c r="G251" s="94">
         <v>0.75</v>
       </c>
-      <c r="H251" s="379"/>
-      <c r="I251" s="380"/>
+      <c r="H251" s="403"/>
+      <c r="I251" s="404"/>
       <c r="J251" s="469"/>
       <c r="K251" s="469"/>
     </row>
@@ -11513,10 +11510,10 @@
       <c r="G252" s="98">
         <v>0.75</v>
       </c>
-      <c r="H252" s="378" t="s">
+      <c r="H252" s="402" t="s">
         <v>35</v>
       </c>
-      <c r="I252" s="378" t="s">
+      <c r="I252" s="402" t="s">
         <v>78</v>
       </c>
       <c r="J252" s="470" t="s">
@@ -11548,8 +11545,8 @@
       <c r="G253" s="101">
         <v>0.75</v>
       </c>
-      <c r="H253" s="379"/>
-      <c r="I253" s="379"/>
+      <c r="H253" s="403"/>
+      <c r="I253" s="403"/>
       <c r="J253" s="469"/>
       <c r="K253" s="469"/>
     </row>
@@ -11575,8 +11572,8 @@
       <c r="G254" s="104">
         <v>0.75</v>
       </c>
-      <c r="H254" s="379"/>
-      <c r="I254" s="380"/>
+      <c r="H254" s="403"/>
+      <c r="I254" s="404"/>
       <c r="J254" s="469"/>
       <c r="K254" s="469"/>
     </row>
@@ -11602,10 +11599,10 @@
       <c r="G255" s="98">
         <v>0.75</v>
       </c>
-      <c r="H255" s="378" t="s">
+      <c r="H255" s="402" t="s">
         <v>79</v>
       </c>
-      <c r="I255" s="378" t="s">
+      <c r="I255" s="402" t="s">
         <v>80</v>
       </c>
       <c r="J255" s="470" t="s">
@@ -11637,8 +11634,8 @@
       <c r="G256" s="101">
         <v>0.75</v>
       </c>
-      <c r="H256" s="379"/>
-      <c r="I256" s="379"/>
+      <c r="H256" s="403"/>
+      <c r="I256" s="403"/>
       <c r="J256" s="469"/>
       <c r="K256" s="469"/>
     </row>
@@ -11664,8 +11661,8 @@
       <c r="G257" s="104">
         <v>0.75</v>
       </c>
-      <c r="H257" s="379"/>
-      <c r="I257" s="379"/>
+      <c r="H257" s="403"/>
+      <c r="I257" s="403"/>
       <c r="J257" s="469"/>
       <c r="K257" s="469"/>
     </row>
@@ -11691,10 +11688,10 @@
       <c r="G258" s="247">
         <v>0.75</v>
       </c>
-      <c r="H258" s="395" t="s">
+      <c r="H258" s="419" t="s">
         <v>57</v>
       </c>
-      <c r="I258" s="395" t="s">
+      <c r="I258" s="419" t="s">
         <v>59</v>
       </c>
       <c r="J258" s="471" t="s">
@@ -11726,8 +11723,8 @@
       <c r="G259" s="248">
         <v>0.75</v>
       </c>
-      <c r="H259" s="395"/>
-      <c r="I259" s="395"/>
+      <c r="H259" s="419"/>
+      <c r="I259" s="419"/>
       <c r="J259" s="472"/>
       <c r="K259" s="469"/>
     </row>
@@ -11753,8 +11750,8 @@
       <c r="G260" s="249">
         <v>0.75</v>
       </c>
-      <c r="H260" s="395"/>
-      <c r="I260" s="395"/>
+      <c r="H260" s="419"/>
+      <c r="I260" s="419"/>
       <c r="J260" s="472"/>
       <c r="K260" s="469"/>
     </row>
@@ -12159,10 +12156,10 @@
       <c r="G272" s="125">
         <v>0.4375</v>
       </c>
-      <c r="H272" s="374" t="s">
+      <c r="H272" s="398" t="s">
         <v>47</v>
       </c>
-      <c r="I272" s="376" t="s">
+      <c r="I272" s="400" t="s">
         <v>48</v>
       </c>
       <c r="J272" s="229" t="s">
@@ -12194,8 +12191,8 @@
       <c r="G273" s="125">
         <v>0.4375</v>
       </c>
-      <c r="H273" s="375"/>
-      <c r="I273" s="377"/>
+      <c r="H273" s="399"/>
+      <c r="I273" s="401"/>
       <c r="J273" s="229" t="s">
         <v>16</v>
       </c>
@@ -14903,7 +14900,7 @@
       <c r="H355" s="178" t="s">
         <v>193</v>
       </c>
-      <c r="I355" s="421" t="s">
+      <c r="I355" s="445" t="s">
         <v>57</v>
       </c>
       <c r="J355" s="178"/>
@@ -14934,7 +14931,7 @@
       <c r="H356" s="178" t="s">
         <v>193</v>
       </c>
-      <c r="I356" s="422"/>
+      <c r="I356" s="446"/>
       <c r="J356" s="178"/>
       <c r="K356" s="172"/>
     </row>
@@ -14963,7 +14960,7 @@
       <c r="H357" s="178" t="s">
         <v>193</v>
       </c>
-      <c r="I357" s="423"/>
+      <c r="I357" s="447"/>
       <c r="J357" s="178"/>
       <c r="K357" s="172"/>
     </row>
@@ -15056,7 +15053,7 @@
       <c r="H360" s="178" t="s">
         <v>145</v>
       </c>
-      <c r="I360" s="360" t="s">
+      <c r="I360" s="384" t="s">
         <v>72</v>
       </c>
       <c r="J360" s="178"/>
@@ -15087,7 +15084,7 @@
       <c r="H361" s="178" t="s">
         <v>145</v>
       </c>
-      <c r="I361" s="361"/>
+      <c r="I361" s="385"/>
       <c r="J361" s="178"/>
       <c r="K361" s="172"/>
     </row>
@@ -15743,7 +15740,7 @@
       <c r="H381" s="178" t="s">
         <v>141</v>
       </c>
-      <c r="I381" s="450" t="s">
+      <c r="I381" s="380" t="s">
         <v>39</v>
       </c>
       <c r="J381" s="178" t="s">
@@ -16007,7 +16004,7 @@
       <c r="H389" s="178" t="s">
         <v>241</v>
       </c>
-      <c r="I389" s="360" t="s">
+      <c r="I389" s="384" t="s">
         <v>84</v>
       </c>
       <c r="J389" s="178" t="s">
@@ -16040,7 +16037,7 @@
       <c r="H390" s="178" t="s">
         <v>241</v>
       </c>
-      <c r="I390" s="361"/>
+      <c r="I390" s="385"/>
       <c r="J390" s="178" t="s">
         <v>98</v>
       </c>
@@ -17595,13 +17592,13 @@
       <c r="I445" s="286" t="s">
         <v>333</v>
       </c>
-      <c r="J445" s="286" t="s">
-        <v>334</v>
+      <c r="J445" s="381" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="446" spans="1:10">
       <c r="A446" s="289" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B446" s="289">
         <v>1</v>
@@ -17625,15 +17622,15 @@
         <v>308</v>
       </c>
       <c r="I446" s="289" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J446" s="289" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="447" spans="1:10">
       <c r="A447" s="289" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B447" s="289">
         <v>1</v>
@@ -17657,15 +17654,15 @@
         <v>308</v>
       </c>
       <c r="I447" s="289" t="s">
-        <v>337</v>
-      </c>
-      <c r="J447" s="289" t="s">
+        <v>336</v>
+      </c>
+      <c r="J447" s="381" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="448" spans="1:10">
       <c r="A448" s="292" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B448" s="292">
         <v>1</v>
@@ -17686,15 +17683,15 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="H448" s="292" t="s">
+        <v>338</v>
+      </c>
+      <c r="I448" s="292" t="s">
         <v>339</v>
-      </c>
-      <c r="I448" s="292" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="449" spans="1:10">
       <c r="A449" s="297" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B449" s="270">
         <v>1</v>
@@ -17715,7 +17712,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="H449" s="270" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I449" s="270" t="s">
         <v>247</v>
@@ -17724,7 +17721,7 @@
     </row>
     <row r="450" spans="1:10">
       <c r="A450" s="303" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B450" s="270">
         <v>1</v>
@@ -17745,16 +17742,16 @@
         <v>0.6875</v>
       </c>
       <c r="H450" s="270" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I450" s="270" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J450" s="270"/>
     </row>
     <row r="451" spans="1:10">
       <c r="A451" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B451" s="300">
         <v>1</v>
@@ -17775,18 +17772,18 @@
         <v>0.4375</v>
       </c>
       <c r="H451" s="300" t="s">
+        <v>345</v>
+      </c>
+      <c r="I451" s="300" t="s">
+        <v>335</v>
+      </c>
+      <c r="J451" s="300" t="s">
         <v>346</v>
-      </c>
-      <c r="I451" s="300" t="s">
-        <v>336</v>
-      </c>
-      <c r="J451" s="300" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="452" spans="1:10">
       <c r="A452" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B452" s="300">
         <v>1</v>
@@ -17807,18 +17804,18 @@
         <v>0.4375</v>
       </c>
       <c r="H452" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I452" s="300" t="s">
-        <v>340</v>
-      </c>
-      <c r="J452" s="300" t="s">
-        <v>347</v>
+        <v>339</v>
+      </c>
+      <c r="J452" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="453" spans="1:10">
       <c r="A453" s="297" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B453" s="270">
         <v>1</v>
@@ -17827,7 +17824,7 @@
         <v>244</v>
       </c>
       <c r="D453" s="270" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E453" s="298">
         <v>46203</v>
@@ -17839,16 +17836,16 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H453" s="270" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I453" s="270" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J453" s="270"/>
     </row>
     <row r="454" spans="1:10">
       <c r="A454" s="297" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B454" s="270">
         <v>1</v>
@@ -17857,7 +17854,7 @@
         <v>244</v>
       </c>
       <c r="D454" s="270" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E454" s="298">
         <v>46199</v>
@@ -17869,16 +17866,16 @@
         <v>0.4375</v>
       </c>
       <c r="H454" s="270" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I454" s="270" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J454" s="270"/>
     </row>
     <row r="455" spans="1:10">
       <c r="A455" s="303" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B455" s="270">
         <v>1</v>
@@ -17899,10 +17896,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H455" s="270" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I455" s="270" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J455" s="270"/>
     </row>
@@ -17913,7 +17910,7 @@
     </row>
     <row r="457" spans="1:10" ht="15.75">
       <c r="A457" s="295" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E457" s="275"/>
       <c r="F457" s="276"/>
@@ -17924,7 +17921,7 @@
     </row>
     <row r="458" spans="1:10" ht="15.75">
       <c r="A458" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -17933,7 +17930,7 @@
         <v>244</v>
       </c>
       <c r="D458" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E458" s="275">
         <v>46195</v>
@@ -17945,18 +17942,18 @@
         <v>0.4375</v>
       </c>
       <c r="H458" s="296" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I458" s="296" t="s">
         <v>263</v>
       </c>
       <c r="J458" s="357" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="459" spans="1:10" ht="15.75">
       <c r="A459" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B459">
         <v>2</v>
@@ -17965,7 +17962,7 @@
         <v>244</v>
       </c>
       <c r="D459" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E459" s="275">
         <v>46195</v>
@@ -17977,18 +17974,18 @@
         <v>0.4375</v>
       </c>
       <c r="H459" s="296" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I459" s="296" t="s">
         <v>315</v>
       </c>
       <c r="J459" s="357" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="460" spans="1:10" ht="15.75">
       <c r="A460" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B460">
         <v>1</v>
@@ -17997,7 +17994,7 @@
         <v>244</v>
       </c>
       <c r="D460" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E460" s="275">
         <v>46195</v>
@@ -18009,7 +18006,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H460" s="296" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I460" s="296" t="s">
         <v>263</v>
@@ -18020,7 +18017,7 @@
     </row>
     <row r="461" spans="1:10" ht="15.75">
       <c r="A461" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -18029,7 +18026,7 @@
         <v>244</v>
       </c>
       <c r="D461" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E461" s="275">
         <v>46196</v>
@@ -18041,7 +18038,7 @@
         <v>0.4375</v>
       </c>
       <c r="H461" s="296" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I461" s="296" t="s">
         <v>315</v>
@@ -18050,7 +18047,7 @@
     </row>
     <row r="462" spans="1:10" ht="15.75">
       <c r="A462" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B462">
         <v>1</v>
@@ -18059,19 +18056,19 @@
         <v>244</v>
       </c>
       <c r="D462" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="E462" s="275">
         <v>46197</v>
       </c>
       <c r="F462" s="276">
-        <v>0.54166666666666663</v>
+        <v>0.375</v>
       </c>
       <c r="G462" s="276">
-        <v>0.60416666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="H462" s="296" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I462" s="357" t="s">
         <v>263</v>
@@ -18080,7 +18077,7 @@
     </row>
     <row r="463" spans="1:10" ht="15.75">
       <c r="A463" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B463">
         <v>1</v>
@@ -18112,7 +18109,7 @@
     </row>
     <row r="464" spans="1:10" ht="15.75">
       <c r="A464" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B464">
         <v>1</v>
@@ -18136,15 +18133,15 @@
         <v>319</v>
       </c>
       <c r="I464" s="296" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J464" s="296" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="465" spans="1:10" ht="15.75">
       <c r="A465" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B465">
         <v>1</v>
@@ -18168,7 +18165,7 @@
         <v>319</v>
       </c>
       <c r="I465" s="296" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J465" s="296" t="s">
         <v>301</v>
@@ -18176,7 +18173,7 @@
     </row>
     <row r="466" spans="1:10" ht="15.75">
       <c r="A466" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B466">
         <v>1</v>
@@ -18197,18 +18194,18 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H466" s="296" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I466" s="296" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J466" s="296" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="467" spans="1:10" ht="15.75">
       <c r="A467" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B467">
         <v>1</v>
@@ -18229,7 +18226,7 @@
         <v>0.4375</v>
       </c>
       <c r="H467" s="296" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I467" s="296" t="s">
         <v>326</v>
@@ -18240,7 +18237,7 @@
     </row>
     <row r="468" spans="1:10" ht="15.75">
       <c r="A468" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B468">
         <v>1</v>
@@ -18249,7 +18246,7 @@
         <v>244</v>
       </c>
       <c r="D468" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E468" s="275">
         <v>46199</v>
@@ -18272,7 +18269,7 @@
     </row>
     <row r="469" spans="1:10" ht="15.75">
       <c r="A469" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B469">
         <v>1</v>
@@ -18299,12 +18296,12 @@
         <v>263</v>
       </c>
       <c r="J469" s="296" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="470" spans="1:10" ht="15.75">
       <c r="A470" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B470">
         <v>1</v>
@@ -18336,7 +18333,7 @@
     </row>
     <row r="471" spans="1:10" ht="15.75">
       <c r="A471" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B471">
         <v>1</v>
@@ -18345,7 +18342,7 @@
         <v>244</v>
       </c>
       <c r="D471" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E471" s="275">
         <v>46202</v>
@@ -18368,7 +18365,7 @@
     </row>
     <row r="472" spans="1:10" ht="15.75">
       <c r="A472" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B472">
         <v>1</v>
@@ -18377,7 +18374,7 @@
         <v>244</v>
       </c>
       <c r="D472" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E472" s="275">
         <v>46202</v>
@@ -18395,12 +18392,12 @@
         <v>263</v>
       </c>
       <c r="J472" s="296" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="473" spans="1:10" ht="15.75">
       <c r="A473" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B473">
         <v>1</v>
@@ -18421,7 +18418,7 @@
         <v>0.6875</v>
       </c>
       <c r="H473" s="296" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I473" s="296" t="s">
         <v>315</v>
@@ -18432,7 +18429,7 @@
     </row>
     <row r="474" spans="1:10" ht="15.75">
       <c r="A474" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B474">
         <v>1</v>
@@ -18453,7 +18450,7 @@
         <v>0.4375</v>
       </c>
       <c r="H474" s="296" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I474" s="296" t="s">
         <v>315</v>
@@ -18464,7 +18461,7 @@
     </row>
     <row r="475" spans="1:10" ht="15.75">
       <c r="A475" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B475">
         <v>1</v>
@@ -18485,18 +18482,18 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H475" s="296" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I475" s="296" t="s">
         <v>315</v>
       </c>
-      <c r="J475" s="296" t="s">
-        <v>384</v>
+      <c r="J475" s="382" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="476" spans="1:10" ht="15.75">
       <c r="A476" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B476">
         <v>1</v>
@@ -18517,7 +18514,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H476" s="296" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I476" s="296" t="s">
         <v>263</v>
@@ -18528,7 +18525,7 @@
     </row>
     <row r="477" spans="1:10" ht="15.75">
       <c r="A477" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B477">
         <v>1</v>
@@ -18549,18 +18546,18 @@
         <v>0.4375</v>
       </c>
       <c r="H477" s="296" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I477" s="296" t="s">
         <v>315</v>
       </c>
       <c r="J477" s="296" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="15.75">
       <c r="A478" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B478">
         <v>2</v>
@@ -18581,18 +18578,18 @@
         <v>0.4375</v>
       </c>
       <c r="H478" s="296" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I478" s="296" t="s">
         <v>263</v>
       </c>
       <c r="J478" s="296" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="479" spans="1:10" ht="15.75">
       <c r="A479" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B479">
         <v>1</v>
@@ -18613,7 +18610,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H479" s="296" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I479" s="296" t="s">
         <v>315</v>
@@ -18628,14 +18625,14 @@
     </row>
     <row r="481" spans="1:10" ht="15.75">
       <c r="A481" s="295" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H481" s="296"/>
       <c r="I481" s="296"/>
     </row>
     <row r="482" spans="1:10" ht="15.75">
       <c r="A482" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B482">
         <v>1</v>
@@ -18656,7 +18653,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H482" s="296" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I482" s="296" t="s">
         <v>263</v>
@@ -18667,7 +18664,7 @@
     </row>
     <row r="483" spans="1:10" ht="15.75">
       <c r="A483" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B483">
         <v>1</v>
@@ -18696,7 +18693,7 @@
     </row>
     <row r="484" spans="1:10" ht="15.75">
       <c r="A484" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -18717,7 +18714,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="H484" s="296" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I484" s="296" t="s">
         <v>263</v>
@@ -18728,7 +18725,7 @@
     </row>
     <row r="485" spans="1:10" ht="15.75">
       <c r="A485" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -18737,7 +18734,7 @@
         <v>244</v>
       </c>
       <c r="D485" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E485" s="275">
         <v>46202</v>
@@ -18749,7 +18746,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="H485" s="296" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="I485" s="296" t="s">
         <v>315</v>
@@ -18889,7 +18886,7 @@
         <v>400</v>
       </c>
       <c r="J491" s="337" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="492" spans="1:10" s="330" customFormat="1" ht="15.75">
@@ -19044,7 +19041,7 @@
         <v>409</v>
       </c>
       <c r="I496" s="337" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J496" s="338"/>
     </row>
@@ -19197,7 +19194,7 @@
         <v>400</v>
       </c>
       <c r="J501" s="338" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="502" spans="1:10" s="330" customFormat="1" ht="15.75">
@@ -19241,7 +19238,7 @@
         <v>244</v>
       </c>
       <c r="D503" s="338" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E503" s="334">
         <v>46196</v>
@@ -19361,7 +19358,7 @@
         <v>244</v>
       </c>
       <c r="D507" s="338" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E507" s="334">
         <v>46203</v>
@@ -19409,7 +19406,7 @@
         <v>400</v>
       </c>
       <c r="J508" s="338" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="509" spans="1:10" s="330" customFormat="1" ht="15.75">
@@ -19611,7 +19608,7 @@
         <v>326</v>
       </c>
       <c r="J518" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="519" spans="1:10" ht="15.75">
@@ -19669,7 +19666,7 @@
         <v>445</v>
       </c>
       <c r="I520" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="521" spans="1:10" ht="15.75">
@@ -19730,7 +19727,7 @@
         <v>326</v>
       </c>
       <c r="J522" s="356" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="523" spans="1:10" ht="15.75">
@@ -19887,7 +19884,7 @@
         <v>311</v>
       </c>
       <c r="I527" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="528" spans="1:10" ht="15.75">
@@ -19948,15 +19945,15 @@
         <v>330</v>
       </c>
       <c r="I529" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J529" s="356" t="s">
-        <v>460</v>
+        <v>317</v>
       </c>
     </row>
     <row r="530" spans="1:10" ht="15.75">
       <c r="A530" s="312" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B530" s="313">
         <v>1</v>
@@ -19977,7 +19974,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H530" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I530" t="s">
         <v>326</v>
@@ -19988,7 +19985,7 @@
     </row>
     <row r="531" spans="1:10" ht="15.75">
       <c r="A531" s="312" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B531" s="313">
         <v>1</v>
@@ -19997,7 +19994,7 @@
         <v>244</v>
       </c>
       <c r="D531" s="314" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E531" s="315">
         <v>46196</v>
@@ -20009,18 +20006,18 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H531" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I531" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J531" s="356" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="532" spans="1:10" ht="15.75">
       <c r="A532" s="312" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B532" s="313">
         <v>1</v>
@@ -20041,18 +20038,18 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="H532" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I532" t="s">
         <v>326</v>
       </c>
       <c r="J532" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="533" spans="1:10" ht="15.75">
       <c r="A533" s="312" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B533" s="313">
         <v>1</v>
@@ -20079,12 +20076,12 @@
         <v>289</v>
       </c>
       <c r="J533" s="356" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="534" spans="1:10" ht="15.75">
       <c r="A534" s="312" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B534" s="313">
         <v>1</v>
@@ -20108,15 +20105,15 @@
         <v>330</v>
       </c>
       <c r="I534" s="356" t="s">
+        <v>465</v>
+      </c>
+      <c r="J534" s="356" t="s">
         <v>466</v>
-      </c>
-      <c r="J534" s="356" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="535" spans="1:10" ht="15.75">
       <c r="A535" s="312" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B535" s="313">
         <v>1</v>
@@ -20137,15 +20134,15 @@
         <v>0.6875</v>
       </c>
       <c r="H535" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I535" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="536" spans="1:10" ht="15.75">
       <c r="A536" s="312" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B536" s="313">
         <v>1</v>
@@ -20174,7 +20171,7 @@
     </row>
     <row r="537" spans="1:10" ht="15.75">
       <c r="A537" s="312" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B537" s="313">
         <v>1</v>
@@ -20203,7 +20200,7 @@
     </row>
     <row r="538" spans="1:10" ht="15.75">
       <c r="A538" s="312" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B538" s="313">
         <v>1</v>
@@ -20212,7 +20209,7 @@
         <v>244</v>
       </c>
       <c r="D538" s="314" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E538" s="315">
         <v>46197</v>
@@ -20224,7 +20221,7 @@
         <v>0.6875</v>
       </c>
       <c r="H538" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I538" t="s">
         <v>326</v>
@@ -20235,7 +20232,7 @@
     </row>
     <row r="539" spans="1:10" ht="15.75">
       <c r="A539" s="312" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B539" s="313">
         <v>1</v>
@@ -20244,7 +20241,7 @@
         <v>244</v>
       </c>
       <c r="D539" s="314" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E539" s="315">
         <v>46197</v>
@@ -20256,10 +20253,10 @@
         <v>0.6875</v>
       </c>
       <c r="H539" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I539" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J539" s="329" t="s">
         <v>255</v>
@@ -20267,7 +20264,7 @@
     </row>
     <row r="540" spans="1:10" ht="15.75">
       <c r="A540" s="312" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B540" s="313">
         <v>1</v>
@@ -20276,7 +20273,7 @@
         <v>244</v>
       </c>
       <c r="D540" s="314" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E540" s="315">
         <v>46197</v>
@@ -20288,18 +20285,18 @@
         <v>0.6875</v>
       </c>
       <c r="H540" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I540" s="356" t="s">
         <v>459</v>
       </c>
       <c r="J540" s="356" t="s">
-        <v>476</v>
+        <v>291</v>
       </c>
     </row>
     <row r="541" spans="1:10" ht="15.75">
       <c r="A541" s="312" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B541" s="313">
         <v>1</v>
@@ -20320,7 +20317,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="H541" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I541" t="s">
         <v>326</v>
@@ -20328,7 +20325,7 @@
     </row>
     <row r="542" spans="1:10" ht="15.75">
       <c r="A542" s="312" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B542" s="313">
         <v>1</v>
@@ -20352,12 +20349,12 @@
         <v>310</v>
       </c>
       <c r="I542" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="543" spans="1:10" ht="15.75">
       <c r="A543" s="312" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B543" s="313">
         <v>1</v>
@@ -20378,7 +20375,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H543" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I543" t="s">
         <v>326</v>
@@ -20386,7 +20383,7 @@
     </row>
     <row r="544" spans="1:10" ht="15.75">
       <c r="A544" s="312" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B544" s="313">
         <v>1</v>
@@ -20415,7 +20412,7 @@
     </row>
     <row r="545" spans="1:10" ht="15.75">
       <c r="A545" s="312" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B545" s="313">
         <v>1</v>
@@ -20444,7 +20441,7 @@
     </row>
     <row r="546" spans="1:10" ht="15.75">
       <c r="A546" s="312" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B546" s="313">
         <v>1</v>
@@ -20468,12 +20465,12 @@
         <v>311</v>
       </c>
       <c r="I546" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="547" spans="1:10" ht="15.75">
       <c r="A547" s="312" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B547" s="313">
         <v>1</v>
@@ -20494,7 +20491,7 @@
         <v>0.6875</v>
       </c>
       <c r="H547" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I547" t="s">
         <v>326</v>
@@ -20505,7 +20502,7 @@
     </row>
     <row r="548" spans="1:10" ht="15.75">
       <c r="A548" s="312" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B548" s="313">
         <v>1</v>
@@ -20526,18 +20523,18 @@
         <v>0.6875</v>
       </c>
       <c r="H548" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I548" s="356" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J548" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="549" spans="1:10" ht="15.75">
       <c r="A549" s="312" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B549" s="313">
         <v>1</v>
@@ -20558,18 +20555,18 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="H549" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I549" t="s">
         <v>326</v>
       </c>
       <c r="J549" s="356" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="550" spans="1:10" ht="15.75">
       <c r="A550" s="312" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B550" s="313">
         <v>1</v>
@@ -20590,10 +20587,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="H550" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I550" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J550" t="s">
         <v>310</v>
@@ -20601,7 +20598,7 @@
     </row>
     <row r="551" spans="1:10" ht="15.75">
       <c r="A551" s="312" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B551" s="313">
         <v>1</v>
@@ -20622,7 +20619,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="H551" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I551" t="s">
         <v>330</v>
@@ -20633,7 +20630,7 @@
     </row>
     <row r="552" spans="1:10" ht="15.75">
       <c r="A552" s="312" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B552" s="313">
         <v>1</v>
@@ -20654,18 +20651,18 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H552" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I552" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J552" s="356" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="553" spans="1:10" ht="15.75">
       <c r="A553" s="312" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B553" s="313">
         <v>1</v>
@@ -20686,18 +20683,18 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H553" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I553" t="s">
         <v>311</v>
       </c>
       <c r="J553" s="356" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="554" spans="1:10" ht="15.75">
       <c r="A554" s="312" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B554" s="313">
         <v>1</v>
@@ -20718,7 +20715,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="H554" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I554" t="s">
         <v>447</v>
@@ -20726,7 +20723,7 @@
     </row>
     <row r="555" spans="1:10" ht="15.75">
       <c r="A555" s="312" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B555" s="313">
         <v>1</v>
@@ -20747,7 +20744,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="H555" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I555" t="s">
         <v>326</v>
@@ -20755,7 +20752,7 @@
     </row>
     <row r="556" spans="1:10" ht="15.75">
       <c r="A556" s="312" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B556" s="313">
         <v>1</v>
@@ -20776,10 +20773,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="H556" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I556" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J556" s="356" t="s">
         <v>459</v>
@@ -20787,7 +20784,7 @@
     </row>
     <row r="557" spans="1:10" ht="15.75">
       <c r="A557" s="312" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B557" s="313">
         <v>1</v>
@@ -20819,7 +20816,7 @@
     </row>
     <row r="558" spans="1:10" ht="15.75">
       <c r="A558" s="312" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B558" s="313">
         <v>1</v>
@@ -20843,15 +20840,15 @@
         <v>311</v>
       </c>
       <c r="I558" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J558" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="559" spans="1:10" ht="15.75">
       <c r="A559" s="312" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B559" s="313">
         <v>1</v>
@@ -20875,7 +20872,7 @@
         <v>310</v>
       </c>
       <c r="I559" s="356" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J559" s="356" t="s">
         <v>459</v>
@@ -20883,7 +20880,7 @@
     </row>
     <row r="560" spans="1:10" ht="15.75">
       <c r="A560" s="312" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B560" s="313">
         <v>1</v>
@@ -20910,12 +20907,12 @@
         <v>326</v>
       </c>
       <c r="J560" s="356" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="561" spans="1:10" ht="15.75">
       <c r="A561" s="312" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B561" s="313">
         <v>1</v>
@@ -20939,7 +20936,7 @@
         <v>310</v>
       </c>
       <c r="I561" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J561" t="s">
         <v>307</v>
@@ -20947,7 +20944,7 @@
     </row>
     <row r="562" spans="1:10" ht="15.75">
       <c r="A562" s="312" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B562" s="313">
         <v>1</v>
@@ -20971,15 +20968,15 @@
         <v>445</v>
       </c>
       <c r="I562" s="356" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J562" s="356" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="563" spans="1:10" ht="15.75">
       <c r="A563" s="312" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B563" s="313">
         <v>1</v>
@@ -21011,7 +21008,7 @@
     </row>
     <row r="564" spans="1:10" ht="15.75">
       <c r="A564" s="312" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B564" s="313">
         <v>1</v>
@@ -21035,7 +21032,7 @@
         <v>445</v>
       </c>
       <c r="I564" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J564" s="356" t="s">
         <v>459</v>
@@ -21043,7 +21040,7 @@
     </row>
     <row r="565" spans="1:10" ht="15.75">
       <c r="A565" s="312" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B565" s="313">
         <v>1</v>
@@ -21072,7 +21069,7 @@
     </row>
     <row r="566" spans="1:10" ht="15.75">
       <c r="A566" s="312" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B566" s="313">
         <v>1</v>
@@ -21101,7 +21098,7 @@
     </row>
     <row r="567" spans="1:10" ht="15.75">
       <c r="A567" s="312" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B567" s="313">
         <v>1</v>
@@ -21122,15 +21119,15 @@
         <v>0.6875</v>
       </c>
       <c r="H567" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I567" s="356" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="568" spans="1:10" ht="15.75">
       <c r="A568" s="312" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B568" s="313">
         <v>1</v>
@@ -21139,7 +21136,7 @@
         <v>244</v>
       </c>
       <c r="D568" s="314" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E568" s="315">
         <v>46202</v>
@@ -21159,7 +21156,7 @@
     </row>
     <row r="569" spans="1:10" ht="15.75">
       <c r="A569" s="312" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B569" s="313">
         <v>2</v>
@@ -21168,7 +21165,7 @@
         <v>244</v>
       </c>
       <c r="D569" s="314" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E569" s="315">
         <v>46202</v>
@@ -21188,7 +21185,7 @@
     </row>
     <row r="570" spans="1:10" ht="15.75">
       <c r="A570" s="312" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B570" s="313">
         <v>1</v>
@@ -21209,18 +21206,18 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="H570" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I570" s="356" t="s">
-        <v>465</v>
-      </c>
-      <c r="J570" s="356" t="s">
-        <v>466</v>
+        <v>464</v>
+      </c>
+      <c r="J570" s="383" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="571" spans="1:10" ht="15.75">
       <c r="A571" s="312" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B571" s="313">
         <v>1</v>
@@ -21241,18 +21238,18 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="H571" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I571" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J571" s="356" t="s">
-        <v>460</v>
+        <v>507</v>
       </c>
     </row>
     <row r="572" spans="1:10" ht="15.75">
       <c r="A572" s="312" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B572" s="313">
         <v>7</v>
@@ -21261,7 +21258,7 @@
         <v>244</v>
       </c>
       <c r="D572" s="314" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E572" s="315">
         <v>46203</v>
@@ -21281,7 +21278,7 @@
     </row>
     <row r="573" spans="1:10" ht="15.75">
       <c r="A573" s="312" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B573" s="313">
         <v>6</v>
@@ -21290,7 +21287,7 @@
         <v>244</v>
       </c>
       <c r="D573" s="314" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E573" s="315">
         <v>46203</v>
@@ -21310,7 +21307,7 @@
     </row>
     <row r="574" spans="1:10" ht="15.75">
       <c r="A574" s="312" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B574" s="313">
         <v>3</v>
@@ -21319,7 +21316,7 @@
         <v>244</v>
       </c>
       <c r="D574" s="314" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E574" s="315">
         <v>46203</v>
@@ -21331,7 +21328,7 @@
         <v>0.6875</v>
       </c>
       <c r="H574" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I574" t="s">
         <v>447</v>
@@ -21395,10 +21392,10 @@
         <v>308</v>
       </c>
       <c r="I576" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J576" s="356" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="577" spans="1:10" ht="15.75">
@@ -21430,12 +21427,12 @@
         <v>289</v>
       </c>
       <c r="J577" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="578" spans="1:10" ht="15.75">
       <c r="A578" s="312" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B578" s="313">
         <v>1</v>
@@ -21456,7 +21453,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H578" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I578" t="s">
         <v>326</v>
@@ -21464,7 +21461,7 @@
     </row>
     <row r="579" spans="1:10" ht="15.75">
       <c r="A579" s="312" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B579" s="313">
         <v>1</v>
@@ -21488,12 +21485,12 @@
         <v>311</v>
       </c>
       <c r="I579" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="580" spans="1:10" ht="15.75">
       <c r="A580" s="312" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B580" s="313">
         <v>3</v>
@@ -21502,7 +21499,7 @@
         <v>244</v>
       </c>
       <c r="D580" s="314" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E580" s="315">
         <v>46204</v>
@@ -21514,7 +21511,7 @@
         <v>0.6875</v>
       </c>
       <c r="H580" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I580" t="s">
         <v>447</v>
@@ -21522,7 +21519,7 @@
     </row>
     <row r="581" spans="1:10" ht="15.75">
       <c r="A581" s="312" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B581" s="313">
         <v>5</v>
@@ -21531,7 +21528,7 @@
         <v>244</v>
       </c>
       <c r="D581" s="314" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E581" s="315">
         <v>46204</v>
@@ -21543,7 +21540,7 @@
         <v>0.6875</v>
       </c>
       <c r="H581" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I581" t="s">
         <v>447</v>
@@ -21551,7 +21548,7 @@
     </row>
     <row r="582" spans="1:10" ht="15.75">
       <c r="A582" s="312" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B582" s="313">
         <v>4</v>
@@ -21560,7 +21557,7 @@
         <v>244</v>
       </c>
       <c r="D582" s="314" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E582" s="315">
         <v>46204</v>
@@ -21580,7 +21577,7 @@
     </row>
     <row r="583" spans="1:10" ht="15.75">
       <c r="A583" s="312" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B583" s="313">
         <v>8</v>
@@ -21589,7 +21586,7 @@
         <v>244</v>
       </c>
       <c r="D583" s="314" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E583" s="315">
         <v>46204</v>
@@ -21609,7 +21606,7 @@
     </row>
     <row r="584" spans="1:10" ht="15.75">
       <c r="A584" s="312" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B584" s="313">
         <v>1</v>
@@ -21618,7 +21615,7 @@
         <v>244</v>
       </c>
       <c r="D584" s="314" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E584" s="315">
         <v>46204</v>
@@ -21630,7 +21627,7 @@
         <v>0.6875</v>
       </c>
       <c r="H584" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I584" t="s">
         <v>447</v>
@@ -21638,7 +21635,7 @@
     </row>
     <row r="585" spans="1:10" ht="15.75">
       <c r="A585" s="312" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B585" s="313">
         <v>2</v>
@@ -21647,7 +21644,7 @@
         <v>244</v>
       </c>
       <c r="D585" s="314" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E585" s="315">
         <v>46204</v>
@@ -21667,7 +21664,7 @@
     </row>
     <row r="586" spans="1:10" ht="15.75">
       <c r="A586" s="318" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B586" s="319">
         <v>4</v>
@@ -21676,7 +21673,7 @@
         <v>244</v>
       </c>
       <c r="D586" s="320" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E586" s="315">
         <v>46204</v>
@@ -21706,153 +21703,153 @@
       <c r="I590" s="326"/>
     </row>
     <row r="591" spans="1:10">
-      <c r="A591" s="447" t="s">
+      <c r="A591" t="s">
+        <v>513</v>
+      </c>
+      <c r="B591">
+        <v>1</v>
+      </c>
+      <c r="C591" t="s">
+        <v>244</v>
+      </c>
+      <c r="D591" t="s">
+        <v>254</v>
+      </c>
+      <c r="E591" s="275">
+        <v>46195</v>
+      </c>
+      <c r="F591" s="276">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G591" s="276">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H591" t="s">
         <v>514</v>
       </c>
-      <c r="B591" s="447">
-        <v>1</v>
-      </c>
-      <c r="C591" s="447" t="s">
+      <c r="I591" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="592" spans="1:10">
+      <c r="A592" t="s">
+        <v>515</v>
+      </c>
+      <c r="B592">
+        <v>1</v>
+      </c>
+      <c r="C592" t="s">
         <v>244</v>
       </c>
-      <c r="D591" s="447" t="s">
+      <c r="D592" t="s">
         <v>254</v>
       </c>
-      <c r="E591" s="448">
-        <v>46195</v>
-      </c>
-      <c r="F591" s="449">
+      <c r="E592" s="275">
+        <v>46196</v>
+      </c>
+      <c r="F592" s="276">
         <v>0.70833333333333337</v>
       </c>
-      <c r="G591" s="449">
+      <c r="G592" s="276">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H591" s="447" t="s">
-        <v>515</v>
-      </c>
-      <c r="I591" s="447" t="s">
+      <c r="H592" t="s">
+        <v>323</v>
+      </c>
+      <c r="I592" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="592" spans="1:10">
-      <c r="A592" s="447" t="s">
+    <row r="593" spans="1:11">
+      <c r="A593" t="s">
         <v>516</v>
       </c>
-      <c r="B592" s="447">
-        <v>1</v>
-      </c>
-      <c r="C592" s="447" t="s">
+      <c r="B593">
+        <v>1</v>
+      </c>
+      <c r="C593" t="s">
         <v>244</v>
       </c>
-      <c r="D592" s="447" t="s">
+      <c r="D593" t="s">
+        <v>268</v>
+      </c>
+      <c r="E593" s="275">
+        <v>46198</v>
+      </c>
+      <c r="F593" s="276">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G593" s="276">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H593" t="s">
+        <v>517</v>
+      </c>
+      <c r="I593" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="594" spans="1:11">
+      <c r="A594" t="s">
+        <v>519</v>
+      </c>
+      <c r="B594">
+        <v>1</v>
+      </c>
+      <c r="C594" t="s">
+        <v>244</v>
+      </c>
+      <c r="D594" t="s">
         <v>254</v>
       </c>
-      <c r="E592" s="448">
-        <v>46196</v>
-      </c>
-      <c r="F592" s="449">
+      <c r="E594" s="275">
+        <v>46199</v>
+      </c>
+      <c r="F594" s="276">
+        <v>0.6875</v>
+      </c>
+      <c r="G594" s="276">
+        <v>0.75</v>
+      </c>
+      <c r="H594" t="s">
+        <v>338</v>
+      </c>
+      <c r="I594" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="595" spans="1:11">
+      <c r="A595" t="s">
+        <v>521</v>
+      </c>
+      <c r="B595">
+        <v>1</v>
+      </c>
+      <c r="C595" t="s">
+        <v>244</v>
+      </c>
+      <c r="D595" t="s">
+        <v>254</v>
+      </c>
+      <c r="E595" s="275">
+        <v>46202</v>
+      </c>
+      <c r="F595" s="276">
         <v>0.70833333333333337</v>
       </c>
-      <c r="G592" s="449">
+      <c r="G595" s="276">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H592" s="447" t="s">
-        <v>323</v>
-      </c>
-      <c r="I592" s="447" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="593" spans="1:11">
-      <c r="A593" s="447" t="s">
-        <v>517</v>
-      </c>
-      <c r="B593" s="447">
-        <v>1</v>
-      </c>
-      <c r="C593" s="447" t="s">
-        <v>244</v>
-      </c>
-      <c r="D593" s="447" t="s">
-        <v>268</v>
-      </c>
-      <c r="E593" s="448">
-        <v>46198</v>
-      </c>
-      <c r="F593" s="449">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="G593" s="449">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="H593" s="447" t="s">
-        <v>518</v>
-      </c>
-      <c r="I593" s="447" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="594" spans="1:11">
-      <c r="A594" s="447" t="s">
-        <v>520</v>
-      </c>
-      <c r="B594" s="447">
-        <v>1</v>
-      </c>
-      <c r="C594" s="447" t="s">
-        <v>244</v>
-      </c>
-      <c r="D594" s="447" t="s">
-        <v>254</v>
-      </c>
-      <c r="E594" s="448">
-        <v>46199</v>
-      </c>
-      <c r="F594" s="449">
-        <v>0.6875</v>
-      </c>
-      <c r="G594" s="449">
-        <v>0.75</v>
-      </c>
-      <c r="H594" s="447" t="s">
-        <v>339</v>
-      </c>
-      <c r="I594" s="447" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="595" spans="1:11">
-      <c r="A595" s="447" t="s">
+      <c r="H595" t="s">
         <v>522</v>
       </c>
-      <c r="B595" s="447">
-        <v>1</v>
-      </c>
-      <c r="C595" s="447" t="s">
-        <v>244</v>
-      </c>
-      <c r="D595" s="447" t="s">
-        <v>254</v>
-      </c>
-      <c r="E595" s="448">
-        <v>46202</v>
-      </c>
-      <c r="F595" s="449">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="G595" s="449">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="H595" s="447" t="s">
-        <v>523</v>
-      </c>
-      <c r="I595" s="447" t="s">
+      <c r="I595" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="596" spans="1:11">
       <c r="A596" s="326" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B596" s="326"/>
       <c r="C596" s="326"/>
@@ -21860,16 +21857,16 @@
     </row>
     <row r="597" spans="1:11">
       <c r="A597" s="342" t="s">
+        <v>524</v>
+      </c>
+      <c r="B597" s="343">
+        <v>1</v>
+      </c>
+      <c r="C597" s="343" t="s">
         <v>525</v>
       </c>
-      <c r="B597" s="343">
-        <v>1</v>
-      </c>
-      <c r="C597" s="343" t="s">
-        <v>526</v>
-      </c>
       <c r="D597" s="343" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E597" s="344">
         <v>46197</v>
@@ -21881,7 +21878,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H597" s="343" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I597" s="344"/>
       <c r="J597" s="345"/>
@@ -21889,13 +21886,13 @@
     </row>
     <row r="598" spans="1:11">
       <c r="A598" s="347" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B598" s="348">
         <v>1</v>
       </c>
       <c r="C598" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D598" s="348" t="s">
         <v>443</v>
@@ -21910,32 +21907,32 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H598" s="348" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I598" s="349"/>
       <c r="J598" s="350"/>
       <c r="K598" s="351"/>
     </row>
     <row r="599" spans="1:11">
-      <c r="A599" s="427" t="s">
-        <v>529</v>
-      </c>
-      <c r="B599" s="428">
-        <v>1</v>
-      </c>
-      <c r="C599" s="428" t="s">
-        <v>526</v>
-      </c>
-      <c r="D599" s="428" t="s">
+      <c r="A599" s="360" t="s">
+        <v>528</v>
+      </c>
+      <c r="B599" s="361">
+        <v>1</v>
+      </c>
+      <c r="C599" s="361" t="s">
+        <v>525</v>
+      </c>
+      <c r="D599" s="361" t="s">
         <v>140</v>
       </c>
-      <c r="E599" s="429">
+      <c r="E599" s="362">
         <v>46199</v>
       </c>
-      <c r="F599" s="430">
+      <c r="F599" s="363">
         <v>0.75</v>
       </c>
-      <c r="G599" s="431">
+      <c r="G599" s="364">
         <v>0.80208333333333337</v>
       </c>
       <c r="H599" s="348" t="s">
@@ -21946,25 +21943,25 @@
       <c r="K599" s="351"/>
     </row>
     <row r="600" spans="1:11">
-      <c r="A600" s="427" t="s">
-        <v>530</v>
-      </c>
-      <c r="B600" s="428">
-        <v>1</v>
-      </c>
-      <c r="C600" s="428" t="s">
-        <v>526</v>
-      </c>
-      <c r="D600" s="428" t="s">
+      <c r="A600" s="360" t="s">
+        <v>529</v>
+      </c>
+      <c r="B600" s="361">
+        <v>1</v>
+      </c>
+      <c r="C600" s="361" t="s">
+        <v>525</v>
+      </c>
+      <c r="D600" s="361" t="s">
         <v>140</v>
       </c>
-      <c r="E600" s="429">
+      <c r="E600" s="362">
         <v>46199</v>
       </c>
-      <c r="F600" s="430">
+      <c r="F600" s="363">
         <v>0.75</v>
       </c>
-      <c r="G600" s="431">
+      <c r="G600" s="364">
         <v>0.80208333333333337</v>
       </c>
       <c r="H600" s="348" t="s">
@@ -21975,25 +21972,25 @@
       <c r="K600" s="351"/>
     </row>
     <row r="601" spans="1:11">
-      <c r="A601" s="427" t="s">
-        <v>531</v>
-      </c>
-      <c r="B601" s="428">
-        <v>1</v>
-      </c>
-      <c r="C601" s="428" t="s">
-        <v>526</v>
-      </c>
-      <c r="D601" s="428" t="s">
+      <c r="A601" s="360" t="s">
+        <v>530</v>
+      </c>
+      <c r="B601" s="361">
+        <v>1</v>
+      </c>
+      <c r="C601" s="361" t="s">
+        <v>525</v>
+      </c>
+      <c r="D601" s="361" t="s">
         <v>140</v>
       </c>
-      <c r="E601" s="429">
+      <c r="E601" s="362">
         <v>46199</v>
       </c>
-      <c r="F601" s="430">
+      <c r="F601" s="363">
         <v>0.75</v>
       </c>
-      <c r="G601" s="431">
+      <c r="G601" s="364">
         <v>0.80208333333333337</v>
       </c>
       <c r="H601" s="348" t="s">
@@ -22005,13 +22002,13 @@
     </row>
     <row r="602" spans="1:11">
       <c r="A602" s="347" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B602" s="348">
         <v>1</v>
       </c>
       <c r="C602" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D602" s="348" t="s">
         <v>405</v>
@@ -22034,19 +22031,19 @@
     </row>
     <row r="603" spans="1:11">
       <c r="A603" s="347" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B603" s="348">
         <v>1</v>
       </c>
       <c r="C603" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D603" s="348" t="s">
         <v>405</v>
       </c>
       <c r="E603" s="349">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="F603" s="350">
         <v>0.75</v>
@@ -22063,13 +22060,13 @@
     </row>
     <row r="604" spans="1:11">
       <c r="A604" s="347" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B604" s="348">
         <v>1</v>
       </c>
       <c r="C604" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D604" s="348" t="s">
         <v>140</v>
@@ -22090,13 +22087,13 @@
     </row>
     <row r="605" spans="1:11">
       <c r="A605" s="347" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B605" s="348">
         <v>1</v>
       </c>
       <c r="C605" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D605" s="348" t="s">
         <v>210</v>
@@ -22119,13 +22116,13 @@
     </row>
     <row r="606" spans="1:11">
       <c r="A606" s="347" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B606" s="348">
         <v>1</v>
       </c>
       <c r="C606" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D606" s="348" t="s">
         <v>405</v>
@@ -22140,7 +22137,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H606" s="348" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I606" s="349"/>
       <c r="J606" s="350"/>
@@ -22148,13 +22145,13 @@
     </row>
     <row r="607" spans="1:11">
       <c r="A607" s="347" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B607" s="348">
         <v>1</v>
       </c>
       <c r="C607" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D607" s="348" t="s">
         <v>181</v>
@@ -22177,13 +22174,13 @@
     </row>
     <row r="608" spans="1:11">
       <c r="A608" s="347" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B608" s="348">
         <v>1</v>
       </c>
       <c r="C608" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D608" s="348" t="s">
         <v>456</v>
@@ -22206,13 +22203,13 @@
     </row>
     <row r="609" spans="1:11">
       <c r="A609" s="347" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B609" s="348">
         <v>1</v>
       </c>
       <c r="C609" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D609" s="348" t="s">
         <v>181</v>
@@ -22235,16 +22232,16 @@
     </row>
     <row r="610" spans="1:11">
       <c r="A610" s="347" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B610" s="348">
         <v>1</v>
       </c>
       <c r="C610" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D610" s="348" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E610" s="349">
         <v>46197</v>
@@ -22264,13 +22261,13 @@
     </row>
     <row r="611" spans="1:11">
       <c r="A611" s="347" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B611" s="348">
         <v>1</v>
       </c>
       <c r="C611" s="348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D611" s="348" t="s">
         <v>458</v>
@@ -22293,16 +22290,16 @@
     </row>
     <row r="612" spans="1:11">
       <c r="A612" s="347" t="s">
+        <v>542</v>
+      </c>
+      <c r="B612" s="348">
+        <v>1</v>
+      </c>
+      <c r="C612" s="348" t="s">
+        <v>525</v>
+      </c>
+      <c r="D612" s="348" t="s">
         <v>543</v>
-      </c>
-      <c r="B612" s="348">
-        <v>1</v>
-      </c>
-      <c r="C612" s="348" t="s">
-        <v>526</v>
-      </c>
-      <c r="D612" s="348" t="s">
-        <v>544</v>
       </c>
       <c r="E612" s="349">
         <v>46202</v>
@@ -22319,25 +22316,25 @@
       <c r="K612" s="351"/>
     </row>
     <row r="613" spans="1:11">
-      <c r="A613" s="442" t="s">
-        <v>545</v>
-      </c>
-      <c r="B613" s="443">
-        <v>1</v>
-      </c>
-      <c r="C613" s="443" t="s">
-        <v>526</v>
-      </c>
-      <c r="D613" s="443" t="s">
+      <c r="A613" s="375" t="s">
+        <v>544</v>
+      </c>
+      <c r="B613" s="376">
+        <v>1</v>
+      </c>
+      <c r="C613" s="376" t="s">
+        <v>525</v>
+      </c>
+      <c r="D613" s="376" t="s">
         <v>449</v>
       </c>
-      <c r="E613" s="444">
+      <c r="E613" s="377">
         <v>46197</v>
       </c>
-      <c r="F613" s="445">
+      <c r="F613" s="378">
         <v>0.75</v>
       </c>
-      <c r="G613" s="446">
+      <c r="G613" s="379">
         <v>0.80208333333333337</v>
       </c>
       <c r="H613" s="348" t="s">
@@ -22348,25 +22345,25 @@
       <c r="K613" s="351"/>
     </row>
     <row r="614" spans="1:11">
-      <c r="A614" s="427" t="s">
+      <c r="A614" s="360" t="s">
+        <v>545</v>
+      </c>
+      <c r="B614" s="361">
+        <v>1</v>
+      </c>
+      <c r="C614" s="361" t="s">
+        <v>525</v>
+      </c>
+      <c r="D614" s="361" t="s">
         <v>546</v>
       </c>
-      <c r="B614" s="428">
-        <v>1</v>
-      </c>
-      <c r="C614" s="428" t="s">
-        <v>526</v>
-      </c>
-      <c r="D614" s="428" t="s">
-        <v>547</v>
-      </c>
-      <c r="E614" s="429">
+      <c r="E614" s="362">
         <v>46198</v>
       </c>
-      <c r="F614" s="430">
+      <c r="F614" s="363">
         <v>0.75</v>
       </c>
-      <c r="G614" s="431">
+      <c r="G614" s="364">
         <v>0.80208333333333337</v>
       </c>
       <c r="H614" s="348"/>
@@ -22375,25 +22372,25 @@
       <c r="K614" s="351"/>
     </row>
     <row r="615" spans="1:11">
-      <c r="A615" s="427" t="s">
-        <v>548</v>
-      </c>
-      <c r="B615" s="428">
-        <v>1</v>
-      </c>
-      <c r="C615" s="428" t="s">
-        <v>526</v>
-      </c>
-      <c r="D615" s="428" t="s">
+      <c r="A615" s="360" t="s">
         <v>547</v>
       </c>
-      <c r="E615" s="429">
+      <c r="B615" s="361">
+        <v>1</v>
+      </c>
+      <c r="C615" s="361" t="s">
+        <v>525</v>
+      </c>
+      <c r="D615" s="361" t="s">
+        <v>546</v>
+      </c>
+      <c r="E615" s="362">
         <v>46198</v>
       </c>
-      <c r="F615" s="430">
+      <c r="F615" s="363">
         <v>0.75</v>
       </c>
-      <c r="G615" s="431">
+      <c r="G615" s="364">
         <v>0.80208333333333337</v>
       </c>
       <c r="H615" s="348"/>
@@ -22402,25 +22399,25 @@
       <c r="K615" s="351"/>
     </row>
     <row r="616" spans="1:11">
-      <c r="A616" s="427" t="s">
-        <v>549</v>
-      </c>
-      <c r="B616" s="428">
-        <v>1</v>
-      </c>
-      <c r="C616" s="428" t="s">
-        <v>526</v>
-      </c>
-      <c r="D616" s="428" t="s">
-        <v>547</v>
-      </c>
-      <c r="E616" s="429">
+      <c r="A616" s="360" t="s">
+        <v>548</v>
+      </c>
+      <c r="B616" s="361">
+        <v>1</v>
+      </c>
+      <c r="C616" s="361" t="s">
+        <v>525</v>
+      </c>
+      <c r="D616" s="361" t="s">
+        <v>546</v>
+      </c>
+      <c r="E616" s="362">
         <v>46198</v>
       </c>
-      <c r="F616" s="430">
+      <c r="F616" s="363">
         <v>0.75</v>
       </c>
-      <c r="G616" s="431">
+      <c r="G616" s="364">
         <v>0.80208333333333337</v>
       </c>
       <c r="H616" s="348"/>
@@ -22429,25 +22426,25 @@
       <c r="K616" s="351"/>
     </row>
     <row r="617" spans="1:11">
-      <c r="A617" s="432" t="s">
-        <v>550</v>
-      </c>
-      <c r="B617" s="433">
-        <v>1</v>
-      </c>
-      <c r="C617" s="433" t="s">
-        <v>526</v>
-      </c>
-      <c r="D617" s="433" t="s">
+      <c r="A617" s="365" t="s">
+        <v>549</v>
+      </c>
+      <c r="B617" s="366">
+        <v>1</v>
+      </c>
+      <c r="C617" s="366" t="s">
+        <v>525</v>
+      </c>
+      <c r="D617" s="366" t="s">
         <v>405</v>
       </c>
-      <c r="E617" s="434">
+      <c r="E617" s="367">
         <v>46199</v>
       </c>
-      <c r="F617" s="435">
+      <c r="F617" s="368">
         <v>0.75</v>
       </c>
-      <c r="G617" s="436">
+      <c r="G617" s="369">
         <v>0.80208333333333337</v>
       </c>
       <c r="H617" s="348" t="s">
@@ -22458,25 +22455,25 @@
       <c r="K617" s="351"/>
     </row>
     <row r="618" spans="1:11">
-      <c r="A618" s="437" t="s">
-        <v>551</v>
-      </c>
-      <c r="B618" s="438">
-        <v>1</v>
-      </c>
-      <c r="C618" s="438" t="s">
-        <v>526</v>
-      </c>
-      <c r="D618" s="438" t="s">
+      <c r="A618" s="370" t="s">
+        <v>550</v>
+      </c>
+      <c r="B618" s="371">
+        <v>1</v>
+      </c>
+      <c r="C618" s="371" t="s">
+        <v>525</v>
+      </c>
+      <c r="D618" s="371" t="s">
         <v>405</v>
       </c>
-      <c r="E618" s="439">
+      <c r="E618" s="372">
         <v>46199</v>
       </c>
-      <c r="F618" s="440">
+      <c r="F618" s="373">
         <v>0.75</v>
       </c>
-      <c r="G618" s="441">
+      <c r="G618" s="374">
         <v>0.80208333333333337</v>
       </c>
       <c r="H618" s="352" t="s">
@@ -22756,120 +22753,120 @@
   <sheetFormatPr defaultColWidth="38.7109375" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="424" t="s">
+      <c r="A1" s="448" t="s">
+        <v>551</v>
+      </c>
+      <c r="B1" s="449"/>
+      <c r="C1" s="449"/>
+      <c r="D1" s="449"/>
+      <c r="E1" s="449"/>
+      <c r="F1" s="448" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="425"/>
-      <c r="C1" s="425"/>
-      <c r="D1" s="425"/>
-      <c r="E1" s="425"/>
-      <c r="F1" s="424" t="s">
+      <c r="G1" s="449"/>
+      <c r="H1" s="449"/>
+      <c r="I1" s="449"/>
+      <c r="J1" s="449"/>
+      <c r="K1" s="448" t="s">
         <v>553</v>
       </c>
-      <c r="G1" s="425"/>
-      <c r="H1" s="425"/>
-      <c r="I1" s="425"/>
-      <c r="J1" s="425"/>
-      <c r="K1" s="424" t="s">
-        <v>554</v>
-      </c>
-      <c r="L1" s="425"/>
-      <c r="M1" s="425"/>
-      <c r="N1" s="425"/>
-      <c r="O1" s="426"/>
+      <c r="L1" s="449"/>
+      <c r="M1" s="449"/>
+      <c r="N1" s="449"/>
+      <c r="O1" s="450"/>
     </row>
     <row r="2" spans="1:15" s="252" customFormat="1" ht="20.25">
       <c r="A2" s="257" t="s">
+        <v>554</v>
+      </c>
+      <c r="B2" s="258" t="s">
         <v>555</v>
       </c>
-      <c r="B2" s="258" t="s">
+      <c r="C2" s="258" t="s">
         <v>556</v>
       </c>
-      <c r="C2" s="258" t="s">
+      <c r="D2" s="258" t="s">
         <v>557</v>
       </c>
-      <c r="D2" s="258" t="s">
+      <c r="E2" s="260" t="s">
         <v>558</v>
       </c>
-      <c r="E2" s="260" t="s">
+      <c r="F2" s="257" t="s">
         <v>559</v>
       </c>
-      <c r="F2" s="257" t="s">
+      <c r="G2" s="258" t="s">
         <v>560</v>
       </c>
-      <c r="G2" s="258" t="s">
+      <c r="H2" s="258" t="s">
         <v>561</v>
       </c>
-      <c r="H2" s="258" t="s">
+      <c r="I2" s="258" t="s">
         <v>562</v>
       </c>
-      <c r="I2" s="258" t="s">
+      <c r="J2" s="260" t="s">
         <v>563</v>
       </c>
-      <c r="J2" s="260" t="s">
+      <c r="K2" s="257" t="s">
+        <v>559</v>
+      </c>
+      <c r="L2" s="258" t="s">
+        <v>560</v>
+      </c>
+      <c r="M2" s="258" t="s">
         <v>564</v>
       </c>
-      <c r="K2" s="257" t="s">
-        <v>560</v>
-      </c>
-      <c r="L2" s="258" t="s">
-        <v>561</v>
-      </c>
-      <c r="M2" s="258" t="s">
+      <c r="N2" s="258" t="s">
         <v>565</v>
       </c>
-      <c r="N2" s="258" t="s">
+      <c r="O2" s="259" t="s">
         <v>566</v>
-      </c>
-      <c r="O2" s="259" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="306.75" customHeight="1">
       <c r="A3" s="253" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" s="254" t="s">
         <v>568</v>
       </c>
-      <c r="B3" s="254" t="s">
+      <c r="C3" s="254" t="s">
         <v>569</v>
       </c>
-      <c r="C3" s="254" t="s">
+      <c r="D3" s="254" t="s">
         <v>570</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="E3" s="256" t="s">
         <v>571</v>
       </c>
-      <c r="E3" s="256" t="s">
+      <c r="F3" s="253" t="s">
         <v>572</v>
       </c>
-      <c r="F3" s="253" t="s">
+      <c r="G3" s="254" t="s">
         <v>573</v>
       </c>
-      <c r="G3" s="254" t="s">
+      <c r="H3" s="254" t="s">
         <v>574</v>
       </c>
-      <c r="H3" s="254" t="s">
+      <c r="I3" s="254" t="s">
         <v>575</v>
       </c>
-      <c r="I3" s="254" t="s">
+      <c r="J3" s="256" t="s">
         <v>576</v>
       </c>
-      <c r="J3" s="256" t="s">
+      <c r="K3" s="253" t="s">
         <v>577</v>
       </c>
-      <c r="K3" s="253" t="s">
+      <c r="L3" s="254" t="s">
         <v>578</v>
       </c>
-      <c r="L3" s="254" t="s">
+      <c r="M3" s="254" t="s">
         <v>579</v>
       </c>
-      <c r="M3" s="254" t="s">
+      <c r="N3" s="254" t="s">
         <v>580</v>
       </c>
-      <c r="N3" s="254" t="s">
+      <c r="O3" s="255" t="s">
         <v>581</v>
-      </c>
-      <c r="O3" s="255" t="s">
-        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -22883,15 +22880,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="46f9de43-f693-4abd-b3da-16a9446d5b24" xsi:nil="true"/>
@@ -22902,7 +22890,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x010100256068D72C9EFB48AF3F54B18B894F64" ma:contentTypeVersion="10" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="43cc1ef052e03bb8a5b634da50b07d31">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="123f497b-f32e-4e02-92f3-8b4fa7417143" xmlns:ns3="46f9de43-f693-4abd-b3da-16a9446d5b24" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a3b51fdaec3d0484dcb0692a12b6b92" ns2:_="" ns3:_="">
     <xsd:import namespace="123f497b-f32e-4e02-92f3-8b4fa7417143"/>
@@ -23091,14 +23079,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B433E-0496-41C4-9F25-23499B75A235}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88D52BA-A6DF-483C-98B0-475005FD20A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88D52BA-A6DF-483C-98B0-475005FD20A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FDAEC64-9782-4808-ADE6-A4491D0F9D2C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FDAEC64-9782-4808-ADE6-A4491D0F9D2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B433E-0496-41C4-9F25-23499B75A235}"/>
 </file>
--- a/25-26-Bahar-Final-OİS.xlsx
+++ b/25-26-Bahar-Final-OİS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EF7BC76-E170-4616-871F-4BD4D0B13657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{016EB8B8-7FB3-42B9-908A-19110CFECB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1192,6 +1192,9 @@
     <t>Dr. Öğr. Üyesi Cevahir Parlak</t>
   </si>
   <si>
+    <t>Arş. Gör. Berke Erdoğan</t>
+  </si>
+  <si>
     <t>Doç.Dr. Nihan Akıncılar Köseoğlu</t>
   </si>
   <si>
@@ -1232,9 +1235,6 @@
   </si>
   <si>
     <t>Dr.Öğr.Üyesi Tuğba Baş</t>
-  </si>
-  <si>
-    <t>Arş. Gör. Berke Erdoğan</t>
   </si>
   <si>
     <t>INTF202</t>
@@ -18542,10 +18542,10 @@
         <v>384</v>
       </c>
       <c r="I477" s="294" t="s">
-        <v>315</v>
+        <v>385</v>
       </c>
       <c r="J477" s="294" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="15.75">
@@ -18577,12 +18577,12 @@
         <v>263</v>
       </c>
       <c r="J478" s="294" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="479" spans="1:10" ht="15.75">
       <c r="A479" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B479">
         <v>1</v>
@@ -18618,14 +18618,14 @@
     </row>
     <row r="481" spans="1:10" ht="15.75">
       <c r="A481" s="293" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H481" s="294"/>
       <c r="I481" s="294"/>
     </row>
     <row r="482" spans="1:10" ht="15.75">
       <c r="A482" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B482">
         <v>1</v>
@@ -18657,7 +18657,7 @@
     </row>
     <row r="483" spans="1:10" ht="15.75">
       <c r="A483" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B483">
         <v>1</v>
@@ -18686,7 +18686,7 @@
     </row>
     <row r="484" spans="1:10" ht="15.75">
       <c r="A484" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -18718,7 +18718,7 @@
     </row>
     <row r="485" spans="1:10" ht="15.75">
       <c r="A485" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -18727,7 +18727,7 @@
         <v>244</v>
       </c>
       <c r="D485" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E485" s="275">
         <v>46202</v>
@@ -18739,7 +18739,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="H485" s="294" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I485" s="294" t="s">
         <v>315</v>
@@ -18747,7 +18747,7 @@
     </row>
     <row r="486" spans="1:10" ht="15.75">
       <c r="A486" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B486">
         <v>1</v>
@@ -18776,7 +18776,7 @@
     </row>
     <row r="488" spans="1:10">
       <c r="A488" s="329" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B488" s="330"/>
       <c r="C488" s="330"/>
@@ -18790,7 +18790,7 @@
     </row>
     <row r="489" spans="1:10" s="328" customFormat="1" ht="15.75">
       <c r="A489" s="331" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B489" s="331">
         <v>1</v>
@@ -18811,10 +18811,10 @@
         <v>0.4375</v>
       </c>
       <c r="H489" s="334" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I489" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J489" s="331"/>
     </row>
@@ -18841,10 +18841,10 @@
         <v>0.4375</v>
       </c>
       <c r="H490" s="334" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I490" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J490" s="331" t="s">
         <v>401</v>
@@ -18876,10 +18876,10 @@
         <v>403</v>
       </c>
       <c r="I491" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J491" s="335" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="492" spans="1:10" s="328" customFormat="1" ht="15.75">
@@ -18908,7 +18908,7 @@
         <v>406</v>
       </c>
       <c r="I492" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J492" s="353" t="s">
         <v>407</v>
@@ -18940,7 +18940,7 @@
         <v>409</v>
       </c>
       <c r="I493" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J493" s="336"/>
     </row>
@@ -18970,7 +18970,7 @@
         <v>412</v>
       </c>
       <c r="I494" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J494" s="336" t="s">
         <v>315</v>
@@ -18999,10 +18999,10 @@
         <v>0.4375</v>
       </c>
       <c r="H495" s="334" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I495" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J495" s="336" t="s">
         <v>317</v>
@@ -19064,7 +19064,7 @@
         <v>412</v>
       </c>
       <c r="I497" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J497" s="336"/>
     </row>
@@ -19094,7 +19094,7 @@
         <v>412</v>
       </c>
       <c r="I498" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J498" s="336"/>
     </row>
@@ -19124,7 +19124,7 @@
         <v>409</v>
       </c>
       <c r="I499" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J499" s="336"/>
     </row>
@@ -19151,7 +19151,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H500" s="334" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I500" s="335" t="s">
         <v>409</v>
@@ -19184,10 +19184,10 @@
         <v>421</v>
       </c>
       <c r="I501" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J501" s="336" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="502" spans="1:10" s="328" customFormat="1" ht="15.75">
@@ -19216,7 +19216,7 @@
         <v>423</v>
       </c>
       <c r="I502" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J502" s="336"/>
     </row>
@@ -19246,7 +19246,7 @@
         <v>423</v>
       </c>
       <c r="I503" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J503" s="336"/>
     </row>
@@ -19276,7 +19276,7 @@
         <v>412</v>
       </c>
       <c r="I504" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J504" s="336"/>
     </row>
@@ -19336,7 +19336,7 @@
         <v>423</v>
       </c>
       <c r="I506" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J506" s="336"/>
     </row>
@@ -19366,7 +19366,7 @@
         <v>421</v>
       </c>
       <c r="I507" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J507" s="336"/>
     </row>
@@ -19396,7 +19396,7 @@
         <v>412</v>
       </c>
       <c r="I508" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J508" s="336" t="s">
         <v>366</v>
@@ -19428,7 +19428,7 @@
         <v>432</v>
       </c>
       <c r="I509" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J509" s="336"/>
     </row>
@@ -19458,7 +19458,7 @@
         <v>432</v>
       </c>
       <c r="I510" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J510" s="336"/>
     </row>
@@ -19488,7 +19488,7 @@
         <v>432</v>
       </c>
       <c r="I511" s="335" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="J511" s="336"/>
     </row>
@@ -19561,7 +19561,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="H515" s="307" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I515" s="307" t="s">
         <v>409</v>
@@ -22873,17 +22873,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="46f9de43-f693-4abd-b3da-16a9446d5b24" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="123f497b-f32e-4e02-92f3-8b4fa7417143">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -22892,7 +22881,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x010100256068D72C9EFB48AF3F54B18B894F64" ma:contentTypeVersion="10" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="43cc1ef052e03bb8a5b634da50b07d31">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="123f497b-f32e-4e02-92f3-8b4fa7417143" xmlns:ns3="46f9de43-f693-4abd-b3da-16a9446d5b24" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a3b51fdaec3d0484dcb0692a12b6b92" ns2:_="" ns3:_="">
     <xsd:import namespace="123f497b-f32e-4e02-92f3-8b4fa7417143"/>
@@ -23081,14 +23070,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="46f9de43-f693-4abd-b3da-16a9446d5b24" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="123f497b-f32e-4e02-92f3-8b4fa7417143">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88D52BA-A6DF-483C-98B0-475005FD20A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B433E-0496-41C4-9F25-23499B75A235}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B433E-0496-41C4-9F25-23499B75A235}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FDAEC64-9782-4808-ADE6-A4491D0F9D2C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FDAEC64-9782-4808-ADE6-A4491D0F9D2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88D52BA-A6DF-483C-98B0-475005FD20A6}"/>
 </file>